--- a/03-Relatorios/99-Avaliacao_IgovTi_Achados/analise_achados_igovti_2026.xlsx
+++ b/03-Relatorios/99-Avaliacao_IgovTi_Achados/analise_achados_igovti_2026.xlsx
@@ -528,7 +528,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -19336,7 +19336,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -22848,10 +22848,6 @@
       <c r="F5" t="n">
         <v>0.18791539800443</v>
       </c>
-      <c r="G5" t="inlineStr"/>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
-      <c r="J5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -22876,20 +22872,16 @@
       <c r="F6" t="n">
         <v>0.18791539800443</v>
       </c>
-      <c r="G6" t="inlineStr"/>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
-      <c r="J6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -23639,7 +23631,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23662,7 +23654,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23731,7 +23723,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23800,7 +23792,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23892,7 +23884,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -24059,7 +24051,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">

--- a/03-Relatorios/99-Avaliacao_IgovTi_Achados/analise_achados_igovti_2026.xlsx
+++ b/03-Relatorios/99-Avaliacao_IgovTi_Achados/analise_achados_igovti_2026.xlsx
@@ -422,7 +422,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ115"/>
+  <dimension ref="A1:AZ114"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -528,7 +528,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -845,10 +845,10 @@
         <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>5.883609180046387</v>
+        <v>5.890364664928844</v>
       </c>
       <c r="AZ2" t="n">
-        <v>0.1163908199536126</v>
+        <v>0.1096353350711556</v>
       </c>
     </row>
     <row r="3">
@@ -1009,10 +1009,10 @@
         <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>5.740789637268885</v>
+        <v>5.740637912887074</v>
       </c>
       <c r="AZ3" t="n">
-        <v>0.2592103627311149</v>
+        <v>0.2593620871129261</v>
       </c>
     </row>
     <row r="4">
@@ -1173,10 +1173,10 @@
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.738971266634218</v>
+        <v>5.738731600040513</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.2610287333657819</v>
+        <v>0.2612683999594871</v>
       </c>
     </row>
     <row r="5">
@@ -1337,10 +1337,10 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.604752347670958</v>
+        <v>5.598021425451632</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.3952476523290418</v>
+        <v>0.4019785745483677</v>
       </c>
     </row>
     <row r="6">
@@ -1501,10 +1501,10 @@
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.732581895574651</v>
+        <v>5.732033218588409</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.2674181044253494</v>
+        <v>0.2679667814115909</v>
       </c>
     </row>
     <row r="7">
@@ -1665,10 +1665,10 @@
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.422170156329278</v>
+        <v>5.406608976156456</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.5778298436707221</v>
+        <v>0.5933910238435436</v>
       </c>
     </row>
     <row r="8">
@@ -1829,10 +1829,10 @@
         <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.639458446777605</v>
+        <v>5.634406022364769</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.3605415532223955</v>
+        <v>0.365593977635231</v>
       </c>
     </row>
     <row r="9">
@@ -1993,10 +1993,10 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.391729458012899</v>
+        <v>5.374696068439792</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.3917294580128994</v>
+        <v>-0.3746960684397918</v>
       </c>
     </row>
     <row r="10">
@@ -2157,10 +2157,10 @@
         <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.779083900567769</v>
+        <v>5.780784209073631</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.7790839005677688</v>
+        <v>-0.780784209073631</v>
       </c>
     </row>
     <row r="11">
@@ -2321,10 +2321,10 @@
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.469815543066709</v>
+        <v>5.456558645979188</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.4698155430667095</v>
+        <v>-0.4565586459791877</v>
       </c>
     </row>
     <row r="12">
@@ -2485,10 +2485,10 @@
         <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.513221359438263</v>
+        <v>5.502063706271665</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.5132213594382629</v>
+        <v>-0.5020637062716649</v>
       </c>
     </row>
     <row r="13">
@@ -2649,10 +2649,10 @@
         <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.719775581537005</v>
+        <v>5.718607550299646</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.7197755815370055</v>
+        <v>-0.7186075502996463</v>
       </c>
     </row>
     <row r="14">
@@ -2813,10 +2813,10 @@
         <v>5</v>
       </c>
       <c r="AY14" t="n">
-        <v>4.968293221936488</v>
+        <v>4.930781103501952</v>
       </c>
       <c r="AZ14" t="n">
-        <v>0.03170677806351208</v>
+        <v>0.06921889649804847</v>
       </c>
     </row>
     <row r="15">
@@ -2977,10 +2977,10 @@
         <v>6</v>
       </c>
       <c r="AY15" t="n">
-        <v>5.717428208297555</v>
+        <v>5.716146650592663</v>
       </c>
       <c r="AZ15" t="n">
-        <v>0.2825717917024448</v>
+        <v>0.2838533494073374</v>
       </c>
     </row>
     <row r="16">
@@ -3141,10 +3141,10 @@
         <v>6</v>
       </c>
       <c r="AY16" t="n">
-        <v>5.873162172362434</v>
+        <v>5.879412406584827</v>
       </c>
       <c r="AZ16" t="n">
-        <v>0.1268378276375657</v>
+        <v>0.1205875934151734</v>
       </c>
     </row>
     <row r="17">
@@ -3305,10 +3305,10 @@
         <v>5</v>
       </c>
       <c r="AY17" t="n">
-        <v>5.820388161009607</v>
+        <v>5.824086075479116</v>
       </c>
       <c r="AZ17" t="n">
-        <v>-0.8203881610096069</v>
+        <v>-0.8240860754791157</v>
       </c>
     </row>
     <row r="18">
@@ -3469,10 +3469,10 @@
         <v>5</v>
       </c>
       <c r="AY18" t="n">
-        <v>5.659178509140329</v>
+        <v>5.655079809930604</v>
       </c>
       <c r="AZ18" t="n">
-        <v>-0.6591785091403288</v>
+        <v>-0.6550798099306041</v>
       </c>
     </row>
     <row r="19">
@@ -3633,10 +3633,10 @@
         <v>6</v>
       </c>
       <c r="AY19" t="n">
-        <v>5.482658644551677</v>
+        <v>5.470022880873726</v>
       </c>
       <c r="AZ19" t="n">
-        <v>0.5173413554483233</v>
+        <v>0.5299771191262739</v>
       </c>
     </row>
     <row r="20">
@@ -3797,10 +3797,10 @@
         <v>6</v>
       </c>
       <c r="AY20" t="n">
-        <v>5.610983866518061</v>
+        <v>5.604554320454085</v>
       </c>
       <c r="AZ20" t="n">
-        <v>0.3890161334819391</v>
+        <v>0.3954456795459151</v>
       </c>
     </row>
     <row r="21">
@@ -3961,10 +3961,10 @@
         <v>6</v>
       </c>
       <c r="AY21" t="n">
-        <v>5.521664670393336</v>
+        <v>5.510915362713047</v>
       </c>
       <c r="AZ21" t="n">
-        <v>0.4783353296066641</v>
+        <v>0.4890846372869531</v>
       </c>
     </row>
     <row r="22">
@@ -4125,10 +4125,10 @@
         <v>6</v>
       </c>
       <c r="AY22" t="n">
-        <v>5.515793141280364</v>
+        <v>5.5047598676981</v>
       </c>
       <c r="AZ22" t="n">
-        <v>0.4842068587196362</v>
+        <v>0.4952401323019</v>
       </c>
     </row>
     <row r="23">
@@ -4289,10 +4289,10 @@
         <v>6</v>
       </c>
       <c r="AY23" t="n">
-        <v>5.535741052967365</v>
+        <v>5.525672524109299</v>
       </c>
       <c r="AZ23" t="n">
-        <v>0.4642589470326355</v>
+        <v>0.4743274758907008</v>
       </c>
     </row>
     <row r="24">
@@ -4453,10 +4453,10 @@
         <v>5</v>
       </c>
       <c r="AY24" t="n">
-        <v>5.791158423586658</v>
+        <v>5.79344269459258</v>
       </c>
       <c r="AZ24" t="n">
-        <v>-0.7911584235866584</v>
+        <v>-0.7934426945925797</v>
       </c>
     </row>
     <row r="25">
@@ -4617,10 +4617,10 @@
         <v>6</v>
       </c>
       <c r="AY25" t="n">
-        <v>5.681783891899276</v>
+        <v>5.678778461202937</v>
       </c>
       <c r="AZ25" t="n">
-        <v>0.3182161081007244</v>
+        <v>0.3212215387970625</v>
       </c>
     </row>
     <row r="26">
@@ -4781,10 +4781,10 @@
         <v>5</v>
       </c>
       <c r="AY26" t="n">
-        <v>5.021256575030294</v>
+        <v>4.986305933520006</v>
       </c>
       <c r="AZ26" t="n">
-        <v>-0.02125657503029377</v>
+        <v>0.01369406647999405</v>
       </c>
     </row>
     <row r="27">
@@ -4945,10 +4945,10 @@
         <v>6</v>
       </c>
       <c r="AY27" t="n">
-        <v>5.893408020015633</v>
+        <v>5.900637408097178</v>
       </c>
       <c r="AZ27" t="n">
-        <v>0.1065919799843673</v>
+        <v>0.09936259190282204</v>
       </c>
     </row>
     <row r="28">
@@ -5109,10 +5109,10 @@
         <v>5</v>
       </c>
       <c r="AY28" t="n">
-        <v>5.607440638419122</v>
+        <v>5.600839730526965</v>
       </c>
       <c r="AZ28" t="n">
-        <v>-0.6074406384191224</v>
+        <v>-0.6008397305269648</v>
       </c>
     </row>
     <row r="29">
@@ -5273,10 +5273,10 @@
         <v>6</v>
       </c>
       <c r="AY29" t="n">
-        <v>5.81788559269556</v>
+        <v>5.821462474968024</v>
       </c>
       <c r="AZ29" t="n">
-        <v>0.1821144073044403</v>
+        <v>0.1785375250319756</v>
       </c>
     </row>
     <row r="30">
@@ -5437,10 +5437,10 @@
         <v>6</v>
       </c>
       <c r="AY30" t="n">
-        <v>5.31991580423426</v>
+        <v>5.299409276986614</v>
       </c>
       <c r="AZ30" t="n">
-        <v>0.6800841957657404</v>
+        <v>0.7005907230133861</v>
       </c>
     </row>
     <row r="31">
@@ -5601,10 +5601,10 @@
         <v>6</v>
       </c>
       <c r="AY31" t="n">
-        <v>5.568972899778192</v>
+        <v>5.560511569176728</v>
       </c>
       <c r="AZ31" t="n">
-        <v>0.431027100221808</v>
+        <v>0.439488430823272</v>
       </c>
     </row>
     <row r="32">
@@ -5765,10 +5765,10 @@
         <v>5</v>
       </c>
       <c r="AY32" t="n">
-        <v>5.914480298210121</v>
+        <v>5.922728808971473</v>
       </c>
       <c r="AZ32" t="n">
-        <v>-0.9144802982101208</v>
+        <v>-0.9227288089714731</v>
       </c>
     </row>
     <row r="33">
@@ -5929,10 +5929,10 @@
         <v>6</v>
       </c>
       <c r="AY33" t="n">
-        <v>5.923776891531218</v>
+        <v>5.932475015239544</v>
       </c>
       <c r="AZ33" t="n">
-        <v>0.07622310846878211</v>
+        <v>0.06752498476045599</v>
       </c>
     </row>
     <row r="34">
@@ -6093,10 +6093,10 @@
         <v>5</v>
       </c>
       <c r="AY34" t="n">
-        <v>5.855441571812216</v>
+        <v>5.860834781191169</v>
       </c>
       <c r="AZ34" t="n">
-        <v>-0.8554415718122161</v>
+        <v>-0.8608347811911692</v>
       </c>
     </row>
     <row r="35">
@@ -6257,10 +6257,10 @@
         <v>6</v>
       </c>
       <c r="AY35" t="n">
-        <v>5.918056836307521</v>
+        <v>5.926478319874976</v>
       </c>
       <c r="AZ35" t="n">
-        <v>0.081943163692479</v>
+        <v>0.07352168012502425</v>
       </c>
     </row>
     <row r="36">
@@ -6421,10 +6421,10 @@
         <v>4</v>
       </c>
       <c r="AY36" t="n">
-        <v>4.615149884893498</v>
+        <v>4.560558626715195</v>
       </c>
       <c r="AZ36" t="n">
-        <v>-0.6151498848934978</v>
+        <v>-0.5605586267151947</v>
       </c>
     </row>
     <row r="37">
@@ -6585,10 +6585,10 @@
         <v>5</v>
       </c>
       <c r="AY37" t="n">
-        <v>5.649649424075072</v>
+        <v>5.645089867875032</v>
       </c>
       <c r="AZ37" t="n">
-        <v>-0.6496494240750721</v>
+        <v>-0.6450898678750319</v>
       </c>
     </row>
     <row r="38">
@@ -6749,10 +6749,10 @@
         <v>6</v>
       </c>
       <c r="AY38" t="n">
-        <v>5.870995624243064</v>
+        <v>5.877141077278298</v>
       </c>
       <c r="AZ38" t="n">
-        <v>0.1290043757569359</v>
+        <v>0.1228589227217016</v>
       </c>
     </row>
     <row r="39">
@@ -6913,10 +6913,10 @@
         <v>6</v>
       </c>
       <c r="AY39" t="n">
-        <v>5.902780993517503</v>
+        <v>5.910463688535528</v>
       </c>
       <c r="AZ39" t="n">
-        <v>0.09721900648249715</v>
+        <v>0.08953631146447183</v>
       </c>
     </row>
     <row r="40">
@@ -7077,10 +7077,10 @@
         <v>5</v>
       </c>
       <c r="AY40" t="n">
-        <v>5.426135919060324</v>
+        <v>5.410766535840098</v>
       </c>
       <c r="AZ40" t="n">
-        <v>-0.4261359190603242</v>
+        <v>-0.4107665358400983</v>
       </c>
     </row>
     <row r="41">
@@ -7241,10 +7241,10 @@
         <v>5</v>
       </c>
       <c r="AY41" t="n">
-        <v>5.463091907878035</v>
+        <v>5.449509834317031</v>
       </c>
       <c r="AZ41" t="n">
-        <v>-0.4630919078780353</v>
+        <v>-0.4495098343170305</v>
       </c>
     </row>
     <row r="42">
@@ -7405,10 +7405,10 @@
         <v>4</v>
       </c>
       <c r="AY42" t="n">
-        <v>4.459221843312613</v>
+        <v>4.397089406998455</v>
       </c>
       <c r="AZ42" t="n">
-        <v>-0.459221843312613</v>
+        <v>-0.3970894069984547</v>
       </c>
     </row>
     <row r="43">
@@ -7569,10 +7569,10 @@
         <v>4</v>
       </c>
       <c r="AY43" t="n">
-        <v>4.403946646505992</v>
+        <v>4.339140925121445</v>
       </c>
       <c r="AZ43" t="n">
-        <v>-0.4039466465059922</v>
+        <v>-0.3391409251214448</v>
       </c>
     </row>
     <row r="44">
@@ -7733,10 +7733,10 @@
         <v>5</v>
       </c>
       <c r="AY44" t="n">
-        <v>5.567518715290023</v>
+        <v>5.558987055681945</v>
       </c>
       <c r="AZ44" t="n">
-        <v>-0.5675187152900234</v>
+        <v>-0.5589870556819445</v>
       </c>
     </row>
     <row r="45">
@@ -7897,10 +7897,10 @@
         <v>6</v>
       </c>
       <c r="AY45" t="n">
-        <v>5.654486610335287</v>
+        <v>5.6501609959131</v>
       </c>
       <c r="AZ45" t="n">
-        <v>0.3455133896647133</v>
+        <v>0.3498390040868999</v>
       </c>
     </row>
     <row r="46">
@@ -8061,10 +8061,10 @@
         <v>6</v>
       </c>
       <c r="AY46" t="n">
-        <v>5.540327734313289</v>
+        <v>5.530481032015292</v>
       </c>
       <c r="AZ46" t="n">
-        <v>0.4596722656867112</v>
+        <v>0.4695189679847083</v>
       </c>
     </row>
     <row r="47">
@@ -8225,10 +8225,10 @@
         <v>6</v>
       </c>
       <c r="AY47" t="n">
-        <v>5.566360178469718</v>
+        <v>5.557772488320563</v>
       </c>
       <c r="AZ47" t="n">
-        <v>0.4336398215302824</v>
+        <v>0.4422275116794374</v>
       </c>
     </row>
     <row r="48">
@@ -8389,10 +8389,10 @@
         <v>6</v>
       </c>
       <c r="AY48" t="n">
-        <v>5.68829556222445</v>
+        <v>5.685605056703765</v>
       </c>
       <c r="AZ48" t="n">
-        <v>0.3117044377755498</v>
+        <v>0.314394943296235</v>
       </c>
     </row>
     <row r="49">
@@ -8553,10 +8553,10 @@
         <v>6</v>
       </c>
       <c r="AY49" t="n">
-        <v>5.768378360080638</v>
+        <v>5.769560914454302</v>
       </c>
       <c r="AZ49" t="n">
-        <v>0.2316216399193625</v>
+        <v>0.2304390855456981</v>
       </c>
     </row>
     <row r="50">
@@ -8717,10 +8717,10 @@
         <v>5</v>
       </c>
       <c r="AY50" t="n">
-        <v>5.595776682513049</v>
+        <v>5.588611668457789</v>
       </c>
       <c r="AZ50" t="n">
-        <v>-0.5957766825130495</v>
+        <v>-0.5886116684577889</v>
       </c>
     </row>
     <row r="51">
@@ -8881,10 +8881,10 @@
         <v>4</v>
       </c>
       <c r="AY51" t="n">
-        <v>4.984703813417788</v>
+        <v>4.947985363603857</v>
       </c>
       <c r="AZ51" t="n">
-        <v>-0.9847038134177879</v>
+        <v>-0.9479853636038573</v>
       </c>
     </row>
     <row r="52">
@@ -9045,10 +9045,10 @@
         <v>5</v>
       </c>
       <c r="AY52" t="n">
-        <v>5.587865447333705</v>
+        <v>5.580317820676136</v>
       </c>
       <c r="AZ52" t="n">
-        <v>-0.587865447333705</v>
+        <v>-0.5803178206761359</v>
       </c>
     </row>
     <row r="53">
@@ -9209,10 +9209,10 @@
         <v>6</v>
       </c>
       <c r="AY53" t="n">
-        <v>5.662866370131558</v>
+        <v>5.658946027658654</v>
       </c>
       <c r="AZ53" t="n">
-        <v>0.3371336298684415</v>
+        <v>0.3410539723413457</v>
       </c>
     </row>
     <row r="54">
@@ -9373,10 +9373,10 @@
         <v>6</v>
       </c>
       <c r="AY54" t="n">
-        <v>5.923776891531218</v>
+        <v>5.932475015239544</v>
       </c>
       <c r="AZ54" t="n">
-        <v>0.07622310846878211</v>
+        <v>0.06752498476045599</v>
       </c>
     </row>
     <row r="55">
@@ -9537,10 +9537,10 @@
         <v>6</v>
       </c>
       <c r="AY55" t="n">
-        <v>5.184016863259705</v>
+        <v>5.156937829155866</v>
       </c>
       <c r="AZ55" t="n">
-        <v>0.8159831367402948</v>
+        <v>0.8430621708441342</v>
       </c>
     </row>
     <row r="56">
@@ -9701,10 +9701,10 @@
         <v>5</v>
       </c>
       <c r="AY56" t="n">
-        <v>5.618546861282002</v>
+        <v>5.612483085801541</v>
       </c>
       <c r="AZ56" t="n">
-        <v>-0.6185468612820024</v>
+        <v>-0.6124830858015411</v>
       </c>
     </row>
     <row r="57">
@@ -9865,10 +9865,10 @@
         <v>5</v>
       </c>
       <c r="AY57" t="n">
-        <v>5.477806969620595</v>
+        <v>5.464936563446391</v>
       </c>
       <c r="AZ57" t="n">
-        <v>-0.4778069696205947</v>
+        <v>-0.4649365634463907</v>
       </c>
     </row>
     <row r="58">
@@ -10029,10 +10029,10 @@
         <v>6</v>
       </c>
       <c r="AY58" t="n">
-        <v>5.731461955939656</v>
+        <v>5.730859115095501</v>
       </c>
       <c r="AZ58" t="n">
-        <v>0.2685380440603442</v>
+        <v>0.2691408849044992</v>
       </c>
     </row>
     <row r="59">
@@ -10193,10 +10193,10 @@
         <v>5</v>
       </c>
       <c r="AY59" t="n">
-        <v>5.460146776707636</v>
+        <v>5.446422267196278</v>
       </c>
       <c r="AZ59" t="n">
-        <v>-0.4601467767076359</v>
+        <v>-0.4464222671962776</v>
       </c>
     </row>
     <row r="60">
@@ -10357,10 +10357,10 @@
         <v>6</v>
       </c>
       <c r="AY60" t="n">
-        <v>5.820388161009607</v>
+        <v>5.824086075479116</v>
       </c>
       <c r="AZ60" t="n">
-        <v>0.1796118389903931</v>
+        <v>0.1759139245208843</v>
       </c>
     </row>
     <row r="61">
@@ -10521,10 +10521,10 @@
         <v>6</v>
       </c>
       <c r="AY61" t="n">
-        <v>5.795997448996841</v>
+        <v>5.798515750727783</v>
       </c>
       <c r="AZ61" t="n">
-        <v>0.2040025510031587</v>
+        <v>0.2014842492722169</v>
       </c>
     </row>
     <row r="62">
@@ -10685,10 +10685,10 @@
         <v>6</v>
       </c>
       <c r="AY62" t="n">
-        <v>5.80175040816507</v>
+        <v>5.804546941376739</v>
       </c>
       <c r="AZ62" t="n">
-        <v>0.1982495918349301</v>
+        <v>0.1954530586232615</v>
       </c>
     </row>
     <row r="63">
@@ -10849,10 +10849,10 @@
         <v>6</v>
       </c>
       <c r="AY63" t="n">
-        <v>5.688980901482831</v>
+        <v>5.686323541157702</v>
       </c>
       <c r="AZ63" t="n">
-        <v>0.3110190985171695</v>
+        <v>0.3136764588422976</v>
       </c>
     </row>
     <row r="64">
@@ -11013,10 +11013,10 @@
         <v>6</v>
       </c>
       <c r="AY64" t="n">
-        <v>5.660847175961816</v>
+        <v>5.656829178809417</v>
       </c>
       <c r="AZ64" t="n">
-        <v>0.3391528240381838</v>
+        <v>0.3431708211905828</v>
       </c>
     </row>
     <row r="65">
@@ -11177,10 +11177,10 @@
         <v>6</v>
       </c>
       <c r="AY65" t="n">
-        <v>5.72753011711392</v>
+        <v>5.726737119985586</v>
       </c>
       <c r="AZ65" t="n">
-        <v>0.2724698828860799</v>
+        <v>0.2732628800144141</v>
       </c>
     </row>
     <row r="66">
@@ -11341,10 +11341,10 @@
         <v>6</v>
       </c>
       <c r="AY66" t="n">
-        <v>5.832450744030115</v>
+        <v>5.836732043543224</v>
       </c>
       <c r="AZ66" t="n">
-        <v>0.1675492559698855</v>
+        <v>0.1632679564567763</v>
       </c>
     </row>
     <row r="67">
@@ -11505,10 +11505,10 @@
         <v>5</v>
       </c>
       <c r="AY67" t="n">
-        <v>5.110983462099688</v>
+        <v>5.080372299441991</v>
       </c>
       <c r="AZ67" t="n">
-        <v>-0.1109834620996883</v>
+        <v>-0.08037229944199087</v>
       </c>
     </row>
     <row r="68">
@@ -11669,10 +11669,10 @@
         <v>6</v>
       </c>
       <c r="AY68" t="n">
-        <v>5.67635659379556</v>
+        <v>5.673088681627759</v>
       </c>
       <c r="AZ68" t="n">
-        <v>0.3236434062044395</v>
+        <v>0.3269113183722405</v>
       </c>
     </row>
     <row r="69">
@@ -11833,10 +11833,10 @@
         <v>4</v>
       </c>
       <c r="AY69" t="n">
-        <v>4.308171863810489</v>
+        <v>4.238734168023472</v>
       </c>
       <c r="AZ69" t="n">
-        <v>-0.3081718638104887</v>
+        <v>-0.2387341680234725</v>
       </c>
     </row>
     <row r="70">
@@ -11997,10 +11997,10 @@
         <v>5</v>
       </c>
       <c r="AY70" t="n">
-        <v>5.641489413078802</v>
+        <v>5.63653521268334</v>
       </c>
       <c r="AZ70" t="n">
-        <v>-0.6414894130788023</v>
+        <v>-0.6365352126833397</v>
       </c>
     </row>
     <row r="71">
@@ -12161,10 +12161,10 @@
         <v>6</v>
       </c>
       <c r="AY71" t="n">
-        <v>4.973974989458986</v>
+        <v>4.936737659449798</v>
       </c>
       <c r="AZ71" t="n">
-        <v>1.026025010541014</v>
+        <v>1.063262340550202</v>
       </c>
     </row>
     <row r="72">
@@ -12325,10 +12325,10 @@
         <v>6</v>
       </c>
       <c r="AY72" t="n">
-        <v>5.834520604192681</v>
+        <v>5.838902008754529</v>
       </c>
       <c r="AZ72" t="n">
-        <v>0.1654793958073189</v>
+        <v>0.1610979912454713</v>
       </c>
     </row>
     <row r="73">
@@ -12489,10 +12489,10 @@
         <v>6</v>
       </c>
       <c r="AY73" t="n">
-        <v>5.474209182198134</v>
+        <v>5.461164775532597</v>
       </c>
       <c r="AZ73" t="n">
-        <v>0.525790817801866</v>
+        <v>0.5388352244674026</v>
       </c>
     </row>
     <row r="74">
@@ -12653,10 +12653,10 @@
         <v>5</v>
       </c>
       <c r="AY74" t="n">
-        <v>5.681508733528247</v>
+        <v>5.678489995294211</v>
       </c>
       <c r="AZ74" t="n">
-        <v>-0.681508733528247</v>
+        <v>-0.6784899952942114</v>
       </c>
     </row>
     <row r="75">
@@ -12817,10 +12817,10 @@
         <v>6</v>
       </c>
       <c r="AY75" t="n">
-        <v>5.923776891531218</v>
+        <v>5.932475015239544</v>
       </c>
       <c r="AZ75" t="n">
-        <v>0.07622310846878211</v>
+        <v>0.06752498476045599</v>
       </c>
     </row>
     <row r="76">
@@ -12981,10 +12981,10 @@
         <v>5</v>
       </c>
       <c r="AY76" t="n">
-        <v>5.762839611227163</v>
+        <v>5.763754294015123</v>
       </c>
       <c r="AZ76" t="n">
-        <v>-0.7628396112271627</v>
+        <v>-0.763754294015123</v>
       </c>
     </row>
     <row r="77">
@@ -13145,10 +13145,10 @@
         <v>5</v>
       </c>
       <c r="AY77" t="n">
-        <v>5.544210476852252</v>
+        <v>5.534551556385189</v>
       </c>
       <c r="AZ77" t="n">
-        <v>-0.5442104768522524</v>
+        <v>-0.534551556385189</v>
       </c>
     </row>
     <row r="78">
@@ -13309,10 +13309,10 @@
         <v>4</v>
       </c>
       <c r="AY78" t="n">
-        <v>4.556762074473257</v>
+        <v>4.499346995288306</v>
       </c>
       <c r="AZ78" t="n">
-        <v>-0.5567620744732569</v>
+        <v>-0.4993469952883061</v>
       </c>
     </row>
     <row r="79">
@@ -13473,10 +13473,10 @@
         <v>6</v>
       </c>
       <c r="AY79" t="n">
-        <v>5.228214853083601</v>
+        <v>5.203273374939098</v>
       </c>
       <c r="AZ79" t="n">
-        <v>0.7717851469163985</v>
+        <v>0.7967266250609022</v>
       </c>
     </row>
     <row r="80">
@@ -13637,10 +13637,10 @@
         <v>6</v>
       </c>
       <c r="AY80" t="n">
-        <v>5.658687903931494</v>
+        <v>5.654565477486843</v>
       </c>
       <c r="AZ80" t="n">
-        <v>0.3413120960685063</v>
+        <v>0.3454345225131572</v>
       </c>
     </row>
     <row r="81">
@@ -13801,10 +13801,10 @@
         <v>6</v>
       </c>
       <c r="AY81" t="n">
-        <v>5.923776891531218</v>
+        <v>5.932475015239544</v>
       </c>
       <c r="AZ81" t="n">
-        <v>0.07622310846878211</v>
+        <v>0.06752498476045599</v>
       </c>
     </row>
     <row r="82">
@@ -13965,10 +13965,10 @@
         <v>5</v>
       </c>
       <c r="AY82" t="n">
-        <v>5.614516091633998</v>
+        <v>5.608257375258802</v>
       </c>
       <c r="AZ82" t="n">
-        <v>-0.6145160916339982</v>
+        <v>-0.6082573752588019</v>
       </c>
     </row>
     <row r="83">
@@ -14129,10 +14129,10 @@
         <v>6</v>
       </c>
       <c r="AY83" t="n">
-        <v>5.923776891531218</v>
+        <v>5.932475015239544</v>
       </c>
       <c r="AZ83" t="n">
-        <v>0.07622310846878211</v>
+        <v>0.06752498476045599</v>
       </c>
     </row>
     <row r="84">
@@ -14293,10 +14293,10 @@
         <v>6</v>
       </c>
       <c r="AY84" t="n">
-        <v>5.58654788795143</v>
+        <v>5.578936539913758</v>
       </c>
       <c r="AZ84" t="n">
-        <v>0.4134521120485699</v>
+        <v>0.4210634600862422</v>
       </c>
     </row>
     <row r="85">
@@ -14457,10 +14457,10 @@
         <v>5</v>
       </c>
       <c r="AY85" t="n">
-        <v>5.739782741186348</v>
+        <v>5.73958232009389</v>
       </c>
       <c r="AZ85" t="n">
-        <v>-0.7397827411863478</v>
+        <v>-0.7395823200938896</v>
       </c>
     </row>
     <row r="86">
@@ -14621,10 +14621,10 @@
         <v>6</v>
       </c>
       <c r="AY86" t="n">
-        <v>5.005231198953302</v>
+        <v>4.969505519069765</v>
       </c>
       <c r="AZ86" t="n">
-        <v>0.994768801046698</v>
+        <v>1.030494480930235</v>
       </c>
     </row>
     <row r="87">
@@ -14785,10 +14785,10 @@
         <v>6</v>
       </c>
       <c r="AY87" t="n">
-        <v>5.76417238080565</v>
+        <v>5.765151520587386</v>
       </c>
       <c r="AZ87" t="n">
-        <v>0.2358276191943496</v>
+        <v>0.234848479412614</v>
       </c>
     </row>
     <row r="88">
@@ -14949,10 +14949,10 @@
         <v>6</v>
       </c>
       <c r="AY88" t="n">
-        <v>5.13713984321376</v>
+        <v>5.107793686692037</v>
       </c>
       <c r="AZ88" t="n">
-        <v>0.8628601567862404</v>
+        <v>0.8922063133079625</v>
       </c>
     </row>
     <row r="89">
@@ -15113,59 +15113,59 @@
         <v>6</v>
       </c>
       <c r="AY89" t="n">
-        <v>5.896216822078552</v>
+        <v>5.903582052799369</v>
       </c>
       <c r="AZ89" t="n">
-        <v>0.1037831779214482</v>
+        <v>0.09641794720063057</v>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>IASERJ</t>
+          <t>FTM</t>
         </is>
       </c>
       <c r="B90" t="n">
-        <v>0.4970205662625881</v>
+        <v>0.1065911597372683</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Intermediário</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>0.5</v>
+        <v>0.1135026920665063</v>
       </c>
       <c r="E90" t="n">
-        <v>0.5</v>
+        <v>0.07466324758506734</v>
       </c>
       <c r="F90" t="n">
-        <v>0.5</v>
+        <v>0.0772395956339562</v>
       </c>
       <c r="G90" t="n">
-        <v>0.5</v>
+        <v>0.1029624262516887</v>
       </c>
       <c r="H90" t="n">
-        <v>0.5</v>
+        <v>0.05293783274500125</v>
       </c>
       <c r="I90" t="n">
         <v>0</v>
       </c>
       <c r="J90" t="n">
-        <v>0.4166666666666665</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K90" t="n">
-        <v>0.4686802611500751</v>
+        <v>0.1406040783450225</v>
       </c>
       <c r="L90" t="n">
-        <v>0.4999999999999994</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="M90" t="n">
-        <v>0.4942955913713882</v>
+        <v>0.1002699075407856</v>
       </c>
       <c r="N90" t="inlineStr">
         <is>
-          <t>IASERJ</t>
+          <t>FTM</t>
         </is>
       </c>
       <c r="O90" t="n">
@@ -15277,66 +15277,66 @@
         <v>6</v>
       </c>
       <c r="AY90" t="n">
-        <v>4.889889586315107</v>
+        <v>5.700023813498868</v>
       </c>
       <c r="AZ90" t="n">
-        <v>1.110110413684893</v>
+        <v>0.2999761865011319</v>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>FTM</t>
+          <t>SEDEC</t>
         </is>
       </c>
       <c r="B91" t="n">
-        <v>0.1065911597372683</v>
+        <v>0.2386495114889209</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Iniciando</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>0.1135026920665063</v>
+        <v>0.1617206576515022</v>
       </c>
       <c r="E91" t="n">
-        <v>0.07466324758506734</v>
+        <v>0.7019275208946145</v>
       </c>
       <c r="F91" t="n">
-        <v>0.0772395956339562</v>
+        <v>0.1562164156680373</v>
       </c>
       <c r="G91" t="n">
-        <v>0.1029624262516887</v>
+        <v>0.15</v>
       </c>
       <c r="H91" t="n">
-        <v>0.05293783274500125</v>
+        <v>0.5036631082916182</v>
       </c>
       <c r="I91" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J91" t="n">
-        <v>0.1249999999999999</v>
+        <v>0.2083333333333334</v>
       </c>
       <c r="K91" t="n">
-        <v>0.1406040783450225</v>
+        <v>0.09335172544209253</v>
       </c>
       <c r="L91" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.3249999999999997</v>
       </c>
       <c r="M91" t="n">
-        <v>0.1002699075407856</v>
+        <v>0.3090082486152058</v>
       </c>
       <c r="N91" t="inlineStr">
         <is>
-          <t>FTM</t>
+          <t>SEDEC</t>
         </is>
       </c>
       <c r="O91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q91" t="n">
         <v>1</v>
@@ -15354,10 +15354,10 @@
         <v>1</v>
       </c>
       <c r="V91" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="W91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X91" t="n">
         <v>0</v>
@@ -15378,25 +15378,25 @@
         <v>1</v>
       </c>
       <c r="AD91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF91" t="n">
         <v>1</v>
       </c>
       <c r="AG91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI91" t="n">
         <v>1</v>
       </c>
       <c r="AJ91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK91" t="n">
         <v>1</v>
@@ -15426,35 +15426,35 @@
         <v>1</v>
       </c>
       <c r="AT91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU91" t="n">
         <v>1</v>
       </c>
       <c r="AV91" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW91" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="AX91" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY91" t="n">
-        <v>5.702049151511701</v>
+        <v>5.41203442826065</v>
       </c>
       <c r="AZ91" t="n">
-        <v>0.2979508484882993</v>
+        <v>-0.4120344282606503</v>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>SEDEC</t>
+          <t>CEPERJ</t>
         </is>
       </c>
       <c r="B92" t="n">
-        <v>0.2386495114889209</v>
+        <v>0.2580680375751482</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -15462,45 +15462,45 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>0.1617206576515022</v>
+        <v>0</v>
       </c>
       <c r="E92" t="n">
-        <v>0.7019275208946145</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F92" t="n">
-        <v>0.1562164156680373</v>
+        <v>0.5</v>
       </c>
       <c r="G92" t="n">
-        <v>0.15</v>
+        <v>0.5</v>
       </c>
       <c r="H92" t="n">
-        <v>0.5036631082916182</v>
+        <v>0.3336996655614665</v>
       </c>
       <c r="I92" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J92" t="n">
-        <v>0.2083333333333334</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="K92" t="n">
-        <v>0.09335172544209253</v>
+        <v>0.2617809480474065</v>
       </c>
       <c r="L92" t="n">
-        <v>0.3249999999999997</v>
+        <v>0.4999999999999994</v>
       </c>
       <c r="M92" t="n">
-        <v>0.3090082486152058</v>
+        <v>0.4940957477347167</v>
       </c>
       <c r="N92" t="inlineStr">
         <is>
-          <t>SEDEC</t>
+          <t>CEPERJ</t>
         </is>
       </c>
       <c r="O92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q92" t="n">
         <v>1</v>
@@ -15518,13 +15518,13 @@
         <v>1</v>
       </c>
       <c r="V92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W92" t="n">
         <v>0</v>
       </c>
       <c r="X92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y92" t="n">
         <v>0</v>
@@ -15539,7 +15539,7 @@
         <v>0</v>
       </c>
       <c r="AC92" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD92" t="n">
         <v>0</v>
@@ -15560,7 +15560,7 @@
         <v>1</v>
       </c>
       <c r="AJ92" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK92" t="n">
         <v>1</v>
@@ -15599,26 +15599,26 @@
         <v>0</v>
       </c>
       <c r="AW92" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AX92" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY92" t="n">
-        <v>5.42734532094292</v>
+        <v>5.369687016562511</v>
       </c>
       <c r="AZ92" t="n">
-        <v>-0.4273453209429201</v>
+        <v>0.6303129834374888</v>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>CEPERJ</t>
+          <t>CEDAE</t>
         </is>
       </c>
       <c r="B93" t="n">
-        <v>0.2580680375751482</v>
+        <v>0.1992386285611383</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -15626,38 +15626,38 @@
         </is>
       </c>
       <c r="D93" t="n">
-        <v>0</v>
+        <v>0.1732561897413833</v>
       </c>
       <c r="E93" t="n">
-        <v>0.9153816527369236</v>
+        <v>0.2818393167261321</v>
       </c>
       <c r="F93" t="n">
-        <v>0.5</v>
+        <v>0.1162286086327428</v>
       </c>
       <c r="G93" t="n">
-        <v>0.5</v>
+        <v>0.1265656387224728</v>
       </c>
       <c r="H93" t="n">
-        <v>0.3336996655614665</v>
+        <v>0.3086466968301532</v>
       </c>
       <c r="I93" t="n">
         <v>0</v>
       </c>
       <c r="J93" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.2416666666666666</v>
       </c>
       <c r="K93" t="n">
-        <v>0.2617809480474065</v>
+        <v>0.3121024776707694</v>
       </c>
       <c r="L93" t="n">
-        <v>0.4999999999999994</v>
+        <v>0.2024225938585991</v>
       </c>
       <c r="M93" t="n">
-        <v>0.4940957477347167</v>
+        <v>0.2230020345086961</v>
       </c>
       <c r="N93" t="inlineStr">
         <is>
-          <t>CEPERJ</t>
+          <t>CEDAE</t>
         </is>
       </c>
       <c r="O93" t="n">
@@ -15682,16 +15682,16 @@
         <v>1</v>
       </c>
       <c r="V93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="W93" t="n">
         <v>0</v>
       </c>
       <c r="X93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z93" t="n">
         <v>1</v>
@@ -15703,19 +15703,19 @@
         <v>0</v>
       </c>
       <c r="AC93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF93" t="n">
         <v>1</v>
       </c>
       <c r="AG93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH93" t="n">
         <v>0</v>
@@ -15724,7 +15724,7 @@
         <v>1</v>
       </c>
       <c r="AJ93" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK93" t="n">
         <v>1</v>
@@ -15733,7 +15733,7 @@
         <v>1</v>
       </c>
       <c r="AM93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN93" t="n">
         <v>1</v>
@@ -15760,68 +15760,68 @@
         <v>1</v>
       </c>
       <c r="AV93" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW93" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AX93" t="n">
         <v>6</v>
       </c>
       <c r="AY93" t="n">
-        <v>5.386951484209912</v>
+        <v>5.497980646697572</v>
       </c>
       <c r="AZ93" t="n">
-        <v>0.613048515790088</v>
+        <v>0.502019353302428</v>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>CEDAE</t>
+          <t>DERRJ</t>
         </is>
       </c>
       <c r="B94" t="n">
-        <v>0.1992386285611383</v>
+        <v>0.04062100822822648</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>0.1732561897413833</v>
+        <v>0</v>
       </c>
       <c r="E94" t="n">
-        <v>0.2818393167261321</v>
+        <v>0.24389994211122</v>
       </c>
       <c r="F94" t="n">
-        <v>0.1162286086327428</v>
+        <v>0.03659820319123575</v>
       </c>
       <c r="G94" t="n">
-        <v>0.1265656387224728</v>
+        <v>0</v>
       </c>
       <c r="H94" t="n">
-        <v>0.3086466968301532</v>
+        <v>0.1026617725722023</v>
       </c>
       <c r="I94" t="n">
         <v>0</v>
       </c>
       <c r="J94" t="n">
-        <v>0.2416666666666666</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K94" t="n">
-        <v>0.3121024776707694</v>
+        <v>0.09544694339318133</v>
       </c>
       <c r="L94" t="n">
-        <v>0.2024225938585991</v>
+        <v>0</v>
       </c>
       <c r="M94" t="n">
-        <v>0.2230020345086961</v>
+        <v>0.07777277505130466</v>
       </c>
       <c r="N94" t="inlineStr">
         <is>
-          <t>CEDAE</t>
+          <t>DERRJ</t>
         </is>
       </c>
       <c r="O94" t="n">
@@ -15852,10 +15852,10 @@
         <v>0</v>
       </c>
       <c r="X94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z94" t="n">
         <v>1</v>
@@ -15879,7 +15879,7 @@
         <v>1</v>
       </c>
       <c r="AG94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH94" t="n">
         <v>0</v>
@@ -15888,7 +15888,7 @@
         <v>1</v>
       </c>
       <c r="AJ94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK94" t="n">
         <v>1</v>
@@ -15897,7 +15897,7 @@
         <v>1</v>
       </c>
       <c r="AM94" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN94" t="n">
         <v>1</v>
@@ -15918,7 +15918,7 @@
         <v>1</v>
       </c>
       <c r="AT94" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU94" t="n">
         <v>1</v>
@@ -15933,20 +15933,20 @@
         <v>6</v>
       </c>
       <c r="AY94" t="n">
-        <v>5.509326659970379</v>
+        <v>5.843889787329056</v>
       </c>
       <c r="AZ94" t="n">
-        <v>0.4906733400296215</v>
+        <v>0.1561102126709439</v>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>DERRJ</t>
+          <t>FSC</t>
         </is>
       </c>
       <c r="B95" t="n">
-        <v>0.04062100822822648</v>
+        <v>0.06614068918152717</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -15954,38 +15954,38 @@
         </is>
       </c>
       <c r="D95" t="n">
-        <v>0</v>
+        <v>0.04911057522779355</v>
       </c>
       <c r="E95" t="n">
-        <v>0.24389994211122</v>
+        <v>0.5326908263684618</v>
       </c>
       <c r="F95" t="n">
-        <v>0.03659820319123575</v>
+        <v>0</v>
       </c>
       <c r="G95" t="n">
         <v>0</v>
       </c>
       <c r="H95" t="n">
-        <v>0.1026617725722023</v>
+        <v>0</v>
       </c>
       <c r="I95" t="n">
         <v>0</v>
       </c>
       <c r="J95" t="n">
-        <v>0.1249999999999999</v>
+        <v>0</v>
       </c>
       <c r="K95" t="n">
-        <v>0.09544694339318133</v>
+        <v>0</v>
       </c>
       <c r="L95" t="n">
         <v>0</v>
       </c>
       <c r="M95" t="n">
-        <v>0.07777277505130466</v>
+        <v>0.08171634449330044</v>
       </c>
       <c r="N95" t="inlineStr">
         <is>
-          <t>DERRJ</t>
+          <t>FSC</t>
         </is>
       </c>
       <c r="O95" t="n">
@@ -16010,7 +16010,7 @@
         <v>1</v>
       </c>
       <c r="V95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="W95" t="n">
         <v>0</v>
@@ -16019,7 +16019,7 @@
         <v>1</v>
       </c>
       <c r="Y95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z95" t="n">
         <v>1</v>
@@ -16034,7 +16034,7 @@
         <v>1</v>
       </c>
       <c r="AD95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE95" t="n">
         <v>1</v>
@@ -16043,10 +16043,10 @@
         <v>1</v>
       </c>
       <c r="AG95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH95" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI95" t="n">
         <v>1</v>
@@ -16088,29 +16088,29 @@
         <v>1</v>
       </c>
       <c r="AV95" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW95" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AX95" t="n">
         <v>6</v>
       </c>
       <c r="AY95" t="n">
-        <v>5.839278286075012</v>
+        <v>5.788237137332048</v>
       </c>
       <c r="AZ95" t="n">
-        <v>0.1607217139249881</v>
+        <v>0.2117628626679524</v>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>FSC</t>
+          <t>UERJ</t>
         </is>
       </c>
       <c r="B96" t="n">
-        <v>0.06614068918152717</v>
+        <v>0.08117211938339576</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -16118,10 +16118,10 @@
         </is>
       </c>
       <c r="D96" t="n">
-        <v>0.04911057522779355</v>
+        <v>0</v>
       </c>
       <c r="E96" t="n">
-        <v>0.5326908263684618</v>
+        <v>0.3136786334522643</v>
       </c>
       <c r="F96" t="n">
         <v>0</v>
@@ -16130,33 +16130,33 @@
         <v>0</v>
       </c>
       <c r="H96" t="n">
-        <v>0</v>
+        <v>0.2088913288526473</v>
       </c>
       <c r="I96" t="n">
         <v>0</v>
       </c>
       <c r="J96" t="n">
-        <v>0</v>
+        <v>0.2416666666666666</v>
       </c>
       <c r="K96" t="n">
-        <v>0</v>
+        <v>0.090827242664782</v>
       </c>
       <c r="L96" t="n">
-        <v>0</v>
+        <v>0.3649829682456654</v>
       </c>
       <c r="M96" t="n">
-        <v>0.08171634449330044</v>
+        <v>0.1554117255232419</v>
       </c>
       <c r="N96" t="inlineStr">
         <is>
-          <t>FSC</t>
+          <t>UERJ</t>
         </is>
       </c>
       <c r="O96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q96" t="n">
         <v>1</v>
@@ -16174,16 +16174,16 @@
         <v>1</v>
       </c>
       <c r="V96" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W96" t="n">
         <v>0</v>
       </c>
       <c r="X96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z96" t="n">
         <v>1</v>
@@ -16198,7 +16198,7 @@
         <v>1</v>
       </c>
       <c r="AD96" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE96" t="n">
         <v>1</v>
@@ -16210,7 +16210,7 @@
         <v>1</v>
       </c>
       <c r="AH96" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI96" t="n">
         <v>1</v>
@@ -16255,26 +16255,26 @@
         <v>0</v>
       </c>
       <c r="AW96" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX96" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY96" t="n">
-        <v>5.786193009606103</v>
+        <v>5.755456989119777</v>
       </c>
       <c r="AZ96" t="n">
-        <v>0.2138069903938966</v>
+        <v>-0.7554569891197769</v>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>UERJ</t>
+          <t>BARRA DO PIRAÍ</t>
         </is>
       </c>
       <c r="B97" t="n">
-        <v>0.08117211938339576</v>
+        <v>0.03712765429561814</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -16285,35 +16285,35 @@
         <v>0</v>
       </c>
       <c r="E97" t="n">
-        <v>0.3136786334522643</v>
+        <v>0</v>
       </c>
       <c r="F97" t="n">
-        <v>0</v>
+        <v>0.1134017968087642</v>
       </c>
       <c r="G97" t="n">
-        <v>0</v>
+        <v>0.15</v>
       </c>
       <c r="H97" t="n">
-        <v>0.2088913288526473</v>
+        <v>0</v>
       </c>
       <c r="I97" t="n">
         <v>0</v>
       </c>
       <c r="J97" t="n">
-        <v>0.2416666666666666</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K97" t="n">
-        <v>0.090827242664782</v>
+        <v>0.1406040783450225</v>
       </c>
       <c r="L97" t="n">
-        <v>0.3649829682456654</v>
+        <v>0</v>
       </c>
       <c r="M97" t="n">
-        <v>0.1554117255232419</v>
+        <v>0.07108441743967478</v>
       </c>
       <c r="N97" t="inlineStr">
         <is>
-          <t>UERJ</t>
+          <t>BARRA DO PIRAÍ</t>
         </is>
       </c>
       <c r="O97" t="n">
@@ -16338,7 +16338,7 @@
         <v>1</v>
       </c>
       <c r="V97" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="W97" t="n">
         <v>0</v>
@@ -16374,7 +16374,7 @@
         <v>1</v>
       </c>
       <c r="AH97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI97" t="n">
         <v>1</v>
@@ -16416,78 +16416,78 @@
         <v>1</v>
       </c>
       <c r="AV97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW97" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AX97" t="n">
         <v>5</v>
       </c>
       <c r="AY97" t="n">
-        <v>5.754925078418034</v>
+        <v>5.851508001838982</v>
       </c>
       <c r="AZ97" t="n">
-        <v>-0.7549250784180339</v>
+        <v>-0.8515080018389822</v>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>BARRA DO PIRAÍ</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="B98" t="n">
-        <v>0.03712765429561814</v>
+        <v>0.6571131403027882</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Intermediário</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>0</v>
+        <v>0.743742274886171</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>0.8307633054738472</v>
       </c>
       <c r="F98" t="n">
-        <v>0.1134017968087642</v>
+        <v>0.4220500554344596</v>
       </c>
       <c r="G98" t="n">
-        <v>0.15</v>
+        <v>0.1337240281536406</v>
       </c>
       <c r="H98" t="n">
-        <v>0</v>
+        <v>0.4992721024499848</v>
       </c>
       <c r="I98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J98" t="n">
-        <v>0.1249999999999999</v>
+        <v>1</v>
       </c>
       <c r="K98" t="n">
-        <v>0.1406040783450225</v>
+        <v>0.6223745730876621</v>
       </c>
       <c r="L98" t="n">
-        <v>0</v>
+        <v>0.9999999999999989</v>
       </c>
       <c r="M98" t="n">
-        <v>0.07108441743967478</v>
+        <v>0.5778825759099899</v>
       </c>
       <c r="N98" t="inlineStr">
         <is>
-          <t>BARRA DO PIRAÍ</t>
+          <t>MPERJ</t>
         </is>
       </c>
       <c r="O98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="P98" t="n">
         <v>0</v>
       </c>
       <c r="Q98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R98" t="n">
         <v>1</v>
@@ -16499,10 +16499,10 @@
         <v>1</v>
       </c>
       <c r="U98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="V98" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="W98" t="n">
         <v>0</v>
@@ -16514,28 +16514,28 @@
         <v>0</v>
       </c>
       <c r="Z98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AA98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB98" t="n">
         <v>0</v>
       </c>
       <c r="AC98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD98" t="n">
         <v>1</v>
       </c>
       <c r="AE98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH98" t="n">
         <v>1</v>
@@ -16568,90 +16568,90 @@
         <v>1</v>
       </c>
       <c r="AR98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV98" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW98" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="AX98" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="AY98" t="n">
-        <v>5.84654505636323</v>
+        <v>4.499459936695778</v>
       </c>
       <c r="AZ98" t="n">
-        <v>-0.8465450563632304</v>
+        <v>-1.499459936695778</v>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>MPERJ</t>
+          <t>ANGRA DOS REIS</t>
         </is>
       </c>
       <c r="B99" t="n">
-        <v>0.6571131403027882</v>
+        <v>0.03808284890422253</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Intermediário</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>0.743742274886171</v>
+        <v>0.0301543374510125</v>
       </c>
       <c r="E99" t="n">
-        <v>0.8307633054738472</v>
+        <v>0.02488774919502245</v>
       </c>
       <c r="F99" t="n">
-        <v>0.4220500554344596</v>
+        <v>0.0257465318779854</v>
       </c>
       <c r="G99" t="n">
-        <v>0.1337240281536406</v>
+        <v>0.0324219417703132</v>
       </c>
       <c r="H99" t="n">
-        <v>0.4992721024499848</v>
+        <v>0.1452880989410023</v>
       </c>
       <c r="I99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J99" t="n">
-        <v>1</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="K99" t="n">
-        <v>0.6223745730876621</v>
+        <v>0.04686802611500751</v>
       </c>
       <c r="L99" t="n">
-        <v>0.9999999999999989</v>
+        <v>0</v>
       </c>
       <c r="M99" t="n">
-        <v>0.5778825759099899</v>
+        <v>0.04533422501750872</v>
       </c>
       <c r="N99" t="inlineStr">
         <is>
-          <t>MPERJ</t>
+          <t>ANGRA DOS REIS</t>
         </is>
       </c>
       <c r="O99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="P99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R99" t="n">
         <v>1</v>
@@ -16663,52 +16663,52 @@
         <v>1</v>
       </c>
       <c r="U99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="W99" t="n">
         <v>0</v>
       </c>
       <c r="X99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y99" t="n">
         <v>0</v>
       </c>
       <c r="Z99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB99" t="n">
         <v>0</v>
       </c>
       <c r="AC99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD99" t="n">
         <v>1</v>
       </c>
       <c r="AE99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI99" t="n">
         <v>1</v>
       </c>
       <c r="AJ99" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK99" t="n">
         <v>1</v>
@@ -16732,80 +16732,80 @@
         <v>1</v>
       </c>
       <c r="AR99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV99" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="AX99" t="n">
-        <v>3</v>
+        <v>6</v>
       </c>
       <c r="AY99" t="n">
-        <v>4.556869805656601</v>
+        <v>5.84942493852291</v>
       </c>
       <c r="AZ99" t="n">
-        <v>-1.556869805656601</v>
+        <v>0.15057506147709</v>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>ANGRA DOS REIS</t>
+          <t>TCE-RJ</t>
         </is>
       </c>
       <c r="B100" t="n">
-        <v>0.03808284890422253</v>
+        <v>0.3787705980140124</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Iniciando</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>0.0301543374510125</v>
+        <v>0.5038560968632533</v>
       </c>
       <c r="E100" t="n">
-        <v>0.02488774919502245</v>
+        <v>0</v>
       </c>
       <c r="F100" t="n">
-        <v>0.0257465318779854</v>
+        <v>0.0509979803806467</v>
       </c>
       <c r="G100" t="n">
-        <v>0.0324219417703132</v>
+        <v>0.0502282515626283</v>
       </c>
       <c r="H100" t="n">
-        <v>0.1452880989410023</v>
+        <v>0.7986485052829118</v>
       </c>
       <c r="I100" t="n">
         <v>0</v>
       </c>
       <c r="J100" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K100" t="n">
-        <v>0.04686802611500751</v>
+        <v>0.4061196989022282</v>
       </c>
       <c r="L100" t="n">
-        <v>0</v>
+        <v>0.2952920839800037</v>
       </c>
       <c r="M100" t="n">
-        <v>0.04533422501750872</v>
+        <v>0.264368039119223</v>
       </c>
       <c r="N100" t="inlineStr">
         <is>
-          <t>ANGRA DOS REIS</t>
+          <t>TCE-RJ</t>
         </is>
       </c>
       <c r="O100" t="n">
@@ -16830,7 +16830,7 @@
         <v>1</v>
       </c>
       <c r="V100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="W100" t="n">
         <v>0</v>
@@ -16845,10 +16845,10 @@
         <v>1</v>
       </c>
       <c r="AA100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB100" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC100" t="n">
         <v>1</v>
@@ -16899,10 +16899,10 @@
         <v>1</v>
       </c>
       <c r="AS100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT100" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU100" t="n">
         <v>1</v>
@@ -16911,65 +16911,65 @@
         <v>1</v>
       </c>
       <c r="AW100" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AX100" t="n">
         <v>6</v>
       </c>
       <c r="AY100" t="n">
-        <v>5.844558089129111</v>
+        <v>5.106462042780931</v>
       </c>
       <c r="AZ100" t="n">
-        <v>0.1554419108708887</v>
+        <v>0.8935379572190687</v>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>TCE-RJ</t>
+          <t>SEDSDH</t>
         </is>
       </c>
       <c r="B101" t="n">
-        <v>0.3787705980140124</v>
+        <v>0.1338878960330976</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>0.5038560968632533</v>
+        <v>0.01637019174259785</v>
       </c>
       <c r="E101" t="n">
-        <v>0</v>
+        <v>0.59520045497346</v>
       </c>
       <c r="F101" t="n">
-        <v>0.0509979803806467</v>
+        <v>0.05198814713129492</v>
       </c>
       <c r="G101" t="n">
-        <v>0.0502282515626283</v>
+        <v>0.08349577659101232</v>
       </c>
       <c r="H101" t="n">
-        <v>0.7986485052829118</v>
+        <v>0.3384200735311504</v>
       </c>
       <c r="I101" t="n">
         <v>0</v>
       </c>
       <c r="J101" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.125</v>
       </c>
       <c r="K101" t="n">
-        <v>0.4061196989022282</v>
+        <v>0.1817278778393327</v>
       </c>
       <c r="L101" t="n">
-        <v>0.2952920839800037</v>
+        <v>0.2546392801713945</v>
       </c>
       <c r="M101" t="n">
-        <v>0.264368039119223</v>
+        <v>0.2413689886454244</v>
       </c>
       <c r="N101" t="inlineStr">
         <is>
-          <t>TCE-RJ</t>
+          <t>SEDSDH</t>
         </is>
       </c>
       <c r="O101" t="n">
@@ -16994,7 +16994,7 @@
         <v>1</v>
       </c>
       <c r="V101" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="W101" t="n">
         <v>0</v>
@@ -17003,25 +17003,25 @@
         <v>1</v>
       </c>
       <c r="Y101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z101" t="n">
         <v>1</v>
       </c>
       <c r="AA101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC101" t="n">
         <v>1</v>
       </c>
       <c r="AD101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF101" t="n">
         <v>1</v>
@@ -17030,13 +17030,13 @@
         <v>1</v>
       </c>
       <c r="AH101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI101" t="n">
         <v>1</v>
       </c>
       <c r="AJ101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK101" t="n">
         <v>1</v>
@@ -17063,38 +17063,38 @@
         <v>1</v>
       </c>
       <c r="AS101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT101" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU101" t="n">
         <v>1</v>
       </c>
       <c r="AV101" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW101" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AX101" t="n">
         <v>6</v>
       </c>
       <c r="AY101" t="n">
-        <v>5.135869630830648</v>
+        <v>5.640495807881856</v>
       </c>
       <c r="AZ101" t="n">
-        <v>0.8641303691693523</v>
+        <v>0.3595041921181439</v>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>SEDSDH</t>
+          <t>SECC</t>
         </is>
       </c>
       <c r="B102" t="n">
-        <v>0.1338878960330976</v>
+        <v>0.07255698196385003</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -17102,38 +17102,38 @@
         </is>
       </c>
       <c r="D102" t="n">
-        <v>0.01637019174259785</v>
+        <v>0.02303967971346885</v>
       </c>
       <c r="E102" t="n">
-        <v>0.59520045497346</v>
+        <v>0.2545285466190942</v>
       </c>
       <c r="F102" t="n">
-        <v>0.05198814713129492</v>
+        <v>0.07624161525330951</v>
       </c>
       <c r="G102" t="n">
-        <v>0.08349577659101232</v>
+        <v>0.1148438835406264</v>
       </c>
       <c r="H102" t="n">
-        <v>0.3384200735311504</v>
+        <v>0.1610330501300481</v>
       </c>
       <c r="I102" t="n">
         <v>0</v>
       </c>
       <c r="J102" t="n">
-        <v>0.125</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K102" t="n">
-        <v>0.1817278778393327</v>
+        <v>0.1127510598597294</v>
       </c>
       <c r="L102" t="n">
-        <v>0.2546392801713945</v>
+        <v>0</v>
       </c>
       <c r="M102" t="n">
-        <v>0.2413689886454244</v>
+        <v>0.1178452538988563</v>
       </c>
       <c r="N102" t="inlineStr">
         <is>
-          <t>SEDSDH</t>
+          <t>SECC</t>
         </is>
       </c>
       <c r="O102" t="n">
@@ -17158,7 +17158,7 @@
         <v>1</v>
       </c>
       <c r="V102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="W102" t="n">
         <v>0</v>
@@ -17167,7 +17167,7 @@
         <v>1</v>
       </c>
       <c r="Y102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z102" t="n">
         <v>1</v>
@@ -17182,7 +17182,7 @@
         <v>1</v>
       </c>
       <c r="AD102" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE102" t="n">
         <v>0</v>
@@ -17194,7 +17194,7 @@
         <v>1</v>
       </c>
       <c r="AH102" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI102" t="n">
         <v>1</v>
@@ -17239,65 +17239,65 @@
         <v>0</v>
       </c>
       <c r="AW102" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AX102" t="n">
         <v>6</v>
       </c>
       <c r="AY102" t="n">
-        <v>5.64526729770974</v>
+        <v>5.774244654544101</v>
       </c>
       <c r="AZ102" t="n">
-        <v>0.35473270229026</v>
+        <v>0.2257553454558989</v>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>SECC</t>
+          <t>DRM</t>
         </is>
       </c>
       <c r="B103" t="n">
-        <v>0.07255698196385003</v>
+        <v>0.1517725747934562</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Iniciando</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>0.02303967971346885</v>
+        <v>0.04991930604584918</v>
       </c>
       <c r="E103" t="n">
-        <v>0.2545285466190942</v>
+        <v>0.5105821077103836</v>
       </c>
       <c r="F103" t="n">
-        <v>0.07624161525330951</v>
+        <v>0.3813632311904742</v>
       </c>
       <c r="G103" t="n">
-        <v>0.1148438835406264</v>
+        <v>0.0324219417703132</v>
       </c>
       <c r="H103" t="n">
-        <v>0.1610330501300481</v>
+        <v>0.2699387820561486</v>
       </c>
       <c r="I103" t="n">
         <v>0</v>
       </c>
       <c r="J103" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.2416666666666666</v>
       </c>
       <c r="K103" t="n">
-        <v>0.1127510598597294</v>
+        <v>0.2641346833908033</v>
       </c>
       <c r="L103" t="n">
         <v>0</v>
       </c>
       <c r="M103" t="n">
-        <v>0.1178452538988563</v>
+        <v>0.2449270545990555</v>
       </c>
       <c r="N103" t="inlineStr">
         <is>
-          <t>SECC</t>
+          <t>DRM</t>
         </is>
       </c>
       <c r="O103" t="n">
@@ -17322,16 +17322,16 @@
         <v>1</v>
       </c>
       <c r="V103" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W103" t="n">
         <v>0</v>
       </c>
       <c r="X103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z103" t="n">
         <v>1</v>
@@ -17346,7 +17346,7 @@
         <v>1</v>
       </c>
       <c r="AD103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE103" t="n">
         <v>0</v>
@@ -17358,7 +17358,7 @@
         <v>1</v>
       </c>
       <c r="AH103" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI103" t="n">
         <v>1</v>
@@ -17376,7 +17376,7 @@
         <v>0</v>
       </c>
       <c r="AN103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AO103" t="n">
         <v>1</v>
@@ -17388,13 +17388,13 @@
         <v>1</v>
       </c>
       <c r="AR103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT103" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU103" t="n">
         <v>1</v>
@@ -17403,26 +17403,26 @@
         <v>0</v>
       </c>
       <c r="AW103" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AX103" t="n">
         <v>6</v>
       </c>
       <c r="AY103" t="n">
-        <v>5.772846029411548</v>
+        <v>5.601493370148385</v>
       </c>
       <c r="AZ103" t="n">
-        <v>0.2271539705884518</v>
+        <v>0.3985066298516147</v>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>DRM</t>
+          <t>MARICÁ</t>
         </is>
       </c>
       <c r="B104" t="n">
-        <v>0.1517725747934562</v>
+        <v>0.2470901566378799</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -17430,19 +17430,19 @@
         </is>
       </c>
       <c r="D104" t="n">
-        <v>0.04991930604584918</v>
+        <v>0.2137699464676057</v>
       </c>
       <c r="E104" t="n">
-        <v>0.5105821077103836</v>
+        <v>0.05</v>
       </c>
       <c r="F104" t="n">
-        <v>0.3813632311904742</v>
+        <v>0.5809666087391273</v>
       </c>
       <c r="G104" t="n">
-        <v>0.0324219417703132</v>
+        <v>0.2812763789334853</v>
       </c>
       <c r="H104" t="n">
-        <v>0.2699387820561486</v>
+        <v>0.1220634782566979</v>
       </c>
       <c r="I104" t="n">
         <v>0</v>
@@ -17451,24 +17451,24 @@
         <v>0.2416666666666666</v>
       </c>
       <c r="K104" t="n">
-        <v>0.2641346833908033</v>
+        <v>0.3140707256338942</v>
       </c>
       <c r="L104" t="n">
-        <v>0</v>
+        <v>0.2523539580099978</v>
       </c>
       <c r="M104" t="n">
-        <v>0.2449270545990555</v>
+        <v>0.2775646508155453</v>
       </c>
       <c r="N104" t="inlineStr">
         <is>
-          <t>DRM</t>
+          <t>MARICÁ</t>
         </is>
       </c>
       <c r="O104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q104" t="n">
         <v>1</v>
@@ -17486,7 +17486,7 @@
         <v>1</v>
       </c>
       <c r="V104" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W104" t="n">
         <v>0</v>
@@ -17495,7 +17495,7 @@
         <v>0</v>
       </c>
       <c r="Y104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z104" t="n">
         <v>1</v>
@@ -17510,10 +17510,10 @@
         <v>1</v>
       </c>
       <c r="AD104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF104" t="n">
         <v>1</v>
@@ -17522,7 +17522,7 @@
         <v>1</v>
       </c>
       <c r="AH104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI104" t="n">
         <v>1</v>
@@ -17537,10 +17537,10 @@
         <v>1</v>
       </c>
       <c r="AM104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AO104" t="n">
         <v>1</v>
@@ -17552,7 +17552,7 @@
         <v>1</v>
       </c>
       <c r="AR104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS104" t="n">
         <v>0</v>
@@ -17567,26 +17567,26 @@
         <v>0</v>
       </c>
       <c r="AW104" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX104" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY104" t="n">
-        <v>5.608064124273183</v>
+        <v>5.393627290997314</v>
       </c>
       <c r="AZ104" t="n">
-        <v>0.3919358757268165</v>
+        <v>-0.3936272909973138</v>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>MARICÁ</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="B105" t="n">
-        <v>0.2470901566378799</v>
+        <v>0.3511163912796449</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -17594,38 +17594,38 @@
         </is>
       </c>
       <c r="D105" t="n">
-        <v>0.2137699464676057</v>
+        <v>0.1842245067119203</v>
       </c>
       <c r="E105" t="n">
-        <v>0.05</v>
+        <v>0.5547995450265401</v>
       </c>
       <c r="F105" t="n">
-        <v>0.5809666087391273</v>
+        <v>0.468643118615104</v>
       </c>
       <c r="G105" t="n">
-        <v>0.2812763789334853</v>
+        <v>0.6607598707337168</v>
       </c>
       <c r="H105" t="n">
-        <v>0.1220634782566979</v>
+        <v>0.5941289376163024</v>
       </c>
       <c r="I105" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J105" t="n">
-        <v>0.2416666666666666</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K105" t="n">
-        <v>0.3140707256338942</v>
+        <v>0.4845677221479929</v>
       </c>
       <c r="L105" t="n">
-        <v>0.2523539580099978</v>
+        <v>0.2655841679600076</v>
       </c>
       <c r="M105" t="n">
-        <v>0.2775646508155453</v>
+        <v>0.5037548572007281</v>
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>MARICÁ</t>
+          <t>SES</t>
         </is>
       </c>
       <c r="O105" t="n">
@@ -17668,7 +17668,7 @@
         <v>1</v>
       </c>
       <c r="AB105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC105" t="n">
         <v>1</v>
@@ -17677,7 +17677,7 @@
         <v>1</v>
       </c>
       <c r="AE105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF105" t="n">
         <v>1</v>
@@ -17692,7 +17692,7 @@
         <v>1</v>
       </c>
       <c r="AJ105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK105" t="n">
         <v>1</v>
@@ -17713,16 +17713,16 @@
         <v>1</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AR105" t="n">
         <v>1</v>
       </c>
       <c r="AS105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU105" t="n">
         <v>1</v>
@@ -17737,20 +17737,20 @@
         <v>5</v>
       </c>
       <c r="AY105" t="n">
-        <v>5.409787343547811</v>
+        <v>5.166769610542024</v>
       </c>
       <c r="AZ105" t="n">
-        <v>-0.4097873435478112</v>
+        <v>-0.1667696105420244</v>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>ITERJ</t>
         </is>
       </c>
       <c r="B106" t="n">
-        <v>0.3511163912796449</v>
+        <v>0.2000509200322302</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -17758,45 +17758,45 @@
         </is>
       </c>
       <c r="D106" t="n">
-        <v>0.1842245067119203</v>
+        <v>0.2364416240455129</v>
       </c>
       <c r="E106" t="n">
-        <v>0.5547995450265401</v>
+        <v>0.2818393167261321</v>
       </c>
       <c r="F106" t="n">
-        <v>0.468643118615104</v>
+        <v>0.09155453743447106</v>
       </c>
       <c r="G106" t="n">
-        <v>0.6607598707337168</v>
+        <v>0.1265656387224728</v>
       </c>
       <c r="H106" t="n">
-        <v>0.5941289376163024</v>
+        <v>0.06929180601605563</v>
       </c>
       <c r="I106" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J106" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="K106" t="n">
-        <v>0.4845677221479929</v>
+        <v>0.2357731193976064</v>
       </c>
       <c r="L106" t="n">
-        <v>0.2655841679600076</v>
+        <v>0.2024225938585991</v>
       </c>
       <c r="M106" t="n">
-        <v>0.5037548572007281</v>
+        <v>0.1667681678554963</v>
       </c>
       <c r="N106" t="inlineStr">
         <is>
-          <t>SES</t>
+          <t>ITERJ</t>
         </is>
       </c>
       <c r="O106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="P106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q106" t="n">
         <v>1</v>
@@ -17814,7 +17814,7 @@
         <v>1</v>
       </c>
       <c r="V106" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W106" t="n">
         <v>0</v>
@@ -17823,7 +17823,7 @@
         <v>0</v>
       </c>
       <c r="Y106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z106" t="n">
         <v>1</v>
@@ -17832,7 +17832,7 @@
         <v>1</v>
       </c>
       <c r="AB106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC106" t="n">
         <v>1</v>
@@ -17841,7 +17841,7 @@
         <v>1</v>
       </c>
       <c r="AE106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF106" t="n">
         <v>1</v>
@@ -17850,13 +17850,13 @@
         <v>1</v>
       </c>
       <c r="AH106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI106" t="n">
         <v>1</v>
       </c>
       <c r="AJ106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK106" t="n">
         <v>1</v>
@@ -17865,7 +17865,7 @@
         <v>1</v>
       </c>
       <c r="AM106" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN106" t="n">
         <v>1</v>
@@ -17877,7 +17877,7 @@
         <v>1</v>
       </c>
       <c r="AQ106" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AR106" t="n">
         <v>1</v>
@@ -17895,26 +17895,26 @@
         <v>0</v>
       </c>
       <c r="AW106" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX106" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AY106" t="n">
-        <v>5.193395083939119</v>
+        <v>5.496209222790708</v>
       </c>
       <c r="AZ106" t="n">
-        <v>-0.1933950839391185</v>
+        <v>0.503790777209292</v>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>ITERJ</t>
+          <t>CODIN</t>
         </is>
       </c>
       <c r="B107" t="n">
-        <v>0.2000509200322302</v>
+        <v>0.2460470495950194</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -17922,38 +17922,38 @@
         </is>
       </c>
       <c r="D107" t="n">
-        <v>0.2364416240455129</v>
+        <v>0.2235205846062349</v>
       </c>
       <c r="E107" t="n">
-        <v>0.2818393167261321</v>
+        <v>0.6814368103037126</v>
       </c>
       <c r="F107" t="n">
-        <v>0.09155453743447106</v>
+        <v>0.03936242287996428</v>
       </c>
       <c r="G107" t="n">
-        <v>0.1265656387224728</v>
+        <v>0.192323654976707</v>
       </c>
       <c r="H107" t="n">
-        <v>0.06929180601605563</v>
+        <v>0.352918884966675</v>
       </c>
       <c r="I107" t="n">
         <v>0</v>
       </c>
       <c r="J107" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K107" t="n">
-        <v>0.2357731193976064</v>
+        <v>0.2281526269588791</v>
       </c>
       <c r="L107" t="n">
-        <v>0.2024225938585991</v>
+        <v>0.1655155321114064</v>
       </c>
       <c r="M107" t="n">
-        <v>0.1667681678554963</v>
+        <v>0.2666496395137506</v>
       </c>
       <c r="N107" t="inlineStr">
         <is>
-          <t>ITERJ</t>
+          <t>CODIN</t>
         </is>
       </c>
       <c r="O107" t="n">
@@ -17978,13 +17978,13 @@
         <v>1</v>
       </c>
       <c r="V107" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="W107" t="n">
         <v>0</v>
       </c>
       <c r="X107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y107" t="n">
         <v>1</v>
@@ -17999,13 +17999,13 @@
         <v>0</v>
       </c>
       <c r="AC107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF107" t="n">
         <v>1</v>
@@ -18014,7 +18014,7 @@
         <v>1</v>
       </c>
       <c r="AH107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI107" t="n">
         <v>1</v>
@@ -18047,7 +18047,7 @@
         <v>1</v>
       </c>
       <c r="AS107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT107" t="n">
         <v>1</v>
@@ -18059,65 +18059,65 @@
         <v>0</v>
       </c>
       <c r="AW107" t="n">
-        <v>21</v>
+        <v>17</v>
       </c>
       <c r="AX107" t="n">
         <v>6</v>
       </c>
       <c r="AY107" t="n">
-        <v>5.507636955565564</v>
+        <v>5.395902071441158</v>
       </c>
       <c r="AZ107" t="n">
-        <v>0.4923630444344358</v>
+        <v>0.6040979285588417</v>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>CODIN</t>
+          <t>PETRÓPOLIS</t>
         </is>
       </c>
       <c r="B108" t="n">
-        <v>0.2460470495950194</v>
+        <v>0.02468900861853542</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>0.2235205846062349</v>
+        <v>0</v>
       </c>
       <c r="E108" t="n">
-        <v>0.6814368103037126</v>
+        <v>0</v>
       </c>
       <c r="F108" t="n">
-        <v>0.03936242287996428</v>
+        <v>0</v>
       </c>
       <c r="G108" t="n">
-        <v>0.192323654976707</v>
+        <v>0</v>
       </c>
       <c r="H108" t="n">
-        <v>0.352918884966675</v>
+        <v>0.07764215469266851</v>
       </c>
       <c r="I108" t="n">
         <v>0</v>
       </c>
       <c r="J108" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.1833333333333333</v>
       </c>
       <c r="K108" t="n">
-        <v>0.2281526269588791</v>
+        <v>0.1922748239527651</v>
       </c>
       <c r="L108" t="n">
-        <v>0.1655155321114064</v>
+        <v>0</v>
       </c>
       <c r="M108" t="n">
-        <v>0.2666496395137506</v>
+        <v>0.04726944990486049</v>
       </c>
       <c r="N108" t="inlineStr">
         <is>
-          <t>CODIN</t>
+          <t>PETRÓPOLIS</t>
         </is>
       </c>
       <c r="O108" t="n">
@@ -18142,7 +18142,7 @@
         <v>1</v>
       </c>
       <c r="V108" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="W108" t="n">
         <v>0</v>
@@ -18163,13 +18163,13 @@
         <v>0</v>
       </c>
       <c r="AC108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF108" t="n">
         <v>1</v>
@@ -18178,7 +18178,7 @@
         <v>1</v>
       </c>
       <c r="AH108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI108" t="n">
         <v>1</v>
@@ -18211,77 +18211,77 @@
         <v>1</v>
       </c>
       <c r="AS108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT108" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU108" t="n">
         <v>1</v>
       </c>
       <c r="AV108" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW108" t="n">
-        <v>17</v>
+        <v>22</v>
       </c>
       <c r="AX108" t="n">
         <v>6</v>
       </c>
       <c r="AY108" t="n">
-        <v>5.411957183596291</v>
+        <v>5.87863387365416</v>
       </c>
       <c r="AZ108" t="n">
-        <v>0.5880428164037088</v>
+        <v>0.1213661263458397</v>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>PETRÓPOLIS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B109" t="n">
-        <v>0.02468900861853542</v>
+        <v>0.3436749796527468</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Iniciando</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>0</v>
+        <v>0.3083610594283083</v>
       </c>
       <c r="E109" t="n">
-        <v>0</v>
+        <v>0.7019275208946145</v>
       </c>
       <c r="F109" t="n">
-        <v>0</v>
+        <v>0.3674641240965996</v>
       </c>
       <c r="G109" t="n">
-        <v>0</v>
+        <v>0.2231695591640398</v>
       </c>
       <c r="H109" t="n">
-        <v>0.07764215469266851</v>
+        <v>0.352918884966675</v>
       </c>
       <c r="I109" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J109" t="n">
-        <v>0.1833333333333333</v>
+        <v>0.4416666666666667</v>
       </c>
       <c r="K109" t="n">
-        <v>0.1922748239527651</v>
+        <v>0.4391741411168048</v>
       </c>
       <c r="L109" t="n">
-        <v>0</v>
+        <v>0.1778865218757386</v>
       </c>
       <c r="M109" t="n">
-        <v>0.04726944990486049</v>
+        <v>0.3759729108713883</v>
       </c>
       <c r="N109" t="inlineStr">
         <is>
-          <t>PETRÓPOLIS</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="O109" t="n">
@@ -18306,13 +18306,13 @@
         <v>1</v>
       </c>
       <c r="V109" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="W109" t="n">
         <v>0</v>
       </c>
       <c r="X109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y109" t="n">
         <v>1</v>
@@ -18321,16 +18321,16 @@
         <v>1</v>
       </c>
       <c r="AA109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC109" t="n">
         <v>1</v>
       </c>
       <c r="AD109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE109" t="n">
         <v>1</v>
@@ -18339,7 +18339,7 @@
         <v>1</v>
       </c>
       <c r="AG109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH109" t="n">
         <v>1</v>
@@ -18357,7 +18357,7 @@
         <v>1</v>
       </c>
       <c r="AM109" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN109" t="n">
         <v>1</v>
@@ -18372,7 +18372,7 @@
         <v>1</v>
       </c>
       <c r="AR109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS109" t="n">
         <v>1</v>
@@ -18384,68 +18384,68 @@
         <v>1</v>
       </c>
       <c r="AV109" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW109" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="AX109" t="n">
         <v>6</v>
       </c>
       <c r="AY109" t="n">
-        <v>5.872419554789564</v>
+        <v>5.182997645583422</v>
       </c>
       <c r="AZ109" t="n">
-        <v>0.1275804452104357</v>
+        <v>0.8170023544165783</v>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SÃO GONÇALO</t>
         </is>
       </c>
       <c r="B110" t="n">
-        <v>0.3436749796527468</v>
+        <v>0.06257817551736433</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Iniciando</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>0.3083610594283083</v>
+        <v>0.03649730793349365</v>
       </c>
       <c r="E110" t="n">
-        <v>0.7019275208946145</v>
+        <v>0.07533675241493264</v>
       </c>
       <c r="F110" t="n">
-        <v>0.3674641240965996</v>
+        <v>0.1121228272460081</v>
       </c>
       <c r="G110" t="n">
-        <v>0.2231695591640398</v>
+        <v>0.09977174843737169</v>
       </c>
       <c r="H110" t="n">
-        <v>0.352918884966675</v>
+        <v>0.05293783274500125</v>
       </c>
       <c r="I110" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J110" t="n">
-        <v>0.4416666666666667</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K110" t="n">
-        <v>0.4391741411168048</v>
+        <v>0.09544694339318133</v>
       </c>
       <c r="L110" t="n">
-        <v>0.1778865218757386</v>
+        <v>0.07639178405141835</v>
       </c>
       <c r="M110" t="n">
-        <v>0.3759729108713883</v>
+        <v>0.08643160391026779</v>
       </c>
       <c r="N110" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>SÃO GONÇALO</t>
         </is>
       </c>
       <c r="O110" t="n">
@@ -18470,31 +18470,31 @@
         <v>1</v>
       </c>
       <c r="V110" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="W110" t="n">
         <v>0</v>
       </c>
       <c r="X110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z110" t="n">
         <v>1</v>
       </c>
       <c r="AA110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC110" t="n">
         <v>1</v>
       </c>
       <c r="AD110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE110" t="n">
         <v>1</v>
@@ -18503,7 +18503,7 @@
         <v>1</v>
       </c>
       <c r="AG110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH110" t="n">
         <v>1</v>
@@ -18521,7 +18521,7 @@
         <v>1</v>
       </c>
       <c r="AM110" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN110" t="n">
         <v>1</v>
@@ -18536,13 +18536,13 @@
         <v>1</v>
       </c>
       <c r="AR110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS110" t="n">
         <v>1</v>
       </c>
       <c r="AT110" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU110" t="n">
         <v>1</v>
@@ -18551,26 +18551,26 @@
         <v>0</v>
       </c>
       <c r="AW110" t="n">
-        <v>18</v>
+        <v>21</v>
       </c>
       <c r="AX110" t="n">
         <v>6</v>
       </c>
       <c r="AY110" t="n">
-        <v>5.208874485670501</v>
+        <v>5.796006173568199</v>
       </c>
       <c r="AZ110" t="n">
-        <v>0.7911255143294991</v>
+        <v>0.2039938264318009</v>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="B111" t="n">
-        <v>0.06257817551736433</v>
+        <v>0.01090053627498748</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -18578,45 +18578,45 @@
         </is>
       </c>
       <c r="D111" t="n">
-        <v>0.03649730793349365</v>
+        <v>0</v>
       </c>
       <c r="E111" t="n">
-        <v>0.07533675241493264</v>
+        <v>0.02488774919502245</v>
       </c>
       <c r="F111" t="n">
-        <v>0.1121228272460081</v>
+        <v>0</v>
       </c>
       <c r="G111" t="n">
-        <v>0.09977174843737169</v>
+        <v>0</v>
       </c>
       <c r="H111" t="n">
-        <v>0.05293783274500125</v>
+        <v>0</v>
       </c>
       <c r="I111" t="n">
         <v>0</v>
       </c>
       <c r="J111" t="n">
-        <v>0.1249999999999999</v>
+        <v>0</v>
       </c>
       <c r="K111" t="n">
-        <v>0.09544694339318133</v>
+        <v>0.0936244700701353</v>
       </c>
       <c r="L111" t="n">
-        <v>0.07639178405141835</v>
+        <v>0</v>
       </c>
       <c r="M111" t="n">
-        <v>0.08643160391026779</v>
+        <v>0.0208701111230444</v>
       </c>
       <c r="N111" t="inlineStr">
         <is>
-          <t>SÃO GONÇALO</t>
+          <t>EMATER</t>
         </is>
       </c>
       <c r="O111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q111" t="n">
         <v>1</v>
@@ -18634,13 +18634,13 @@
         <v>1</v>
       </c>
       <c r="V111" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="W111" t="n">
         <v>0</v>
       </c>
       <c r="X111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y111" t="n">
         <v>0</v>
@@ -18706,7 +18706,7 @@
         <v>1</v>
       </c>
       <c r="AT111" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU111" t="n">
         <v>1</v>
@@ -18715,69 +18715,69 @@
         <v>0</v>
       </c>
       <c r="AW111" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AX111" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY111" t="n">
-        <v>5.793603643897826</v>
+        <v>5.908703412012933</v>
       </c>
       <c r="AZ111" t="n">
-        <v>0.2063963561021742</v>
+        <v>-0.9087034120129331</v>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="B112" t="n">
-        <v>0.01090053627498748</v>
+        <v>0.7080605644597759</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Inexpressivo</t>
+          <t>Aprimorado</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>0</v>
+        <v>0.6979978763983506</v>
       </c>
       <c r="E112" t="n">
-        <v>0.02488774919502245</v>
+        <v>1</v>
       </c>
       <c r="F112" t="n">
-        <v>0</v>
+        <v>0.7239640169365842</v>
       </c>
       <c r="G112" t="n">
-        <v>0</v>
+        <v>0.4726402015595599</v>
       </c>
       <c r="H112" t="n">
-        <v>0</v>
+        <v>0.774131913621328</v>
       </c>
       <c r="I112" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J112" t="n">
-        <v>0</v>
+        <v>0.4416666666666667</v>
       </c>
       <c r="K112" t="n">
-        <v>0.0936244700701353</v>
+        <v>0.4870785579360365</v>
       </c>
       <c r="L112" t="n">
-        <v>0</v>
+        <v>0.8957216940728419</v>
       </c>
       <c r="M112" t="n">
-        <v>0.0208701111230444</v>
+        <v>0.7172638476075258</v>
       </c>
       <c r="N112" t="inlineStr">
         <is>
-          <t>EMATER</t>
+          <t>PGE</t>
         </is>
       </c>
       <c r="O112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="P112" t="n">
         <v>0</v>
@@ -18786,7 +18786,7 @@
         <v>1</v>
       </c>
       <c r="R112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S112" t="n">
         <v>1</v>
@@ -18798,7 +18798,7 @@
         <v>1</v>
       </c>
       <c r="V112" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="W112" t="n">
         <v>0</v>
@@ -18813,34 +18813,34 @@
         <v>1</v>
       </c>
       <c r="AA112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB112" t="n">
         <v>0</v>
       </c>
       <c r="AC112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AG112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI112" t="n">
         <v>1</v>
       </c>
       <c r="AJ112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK112" t="n">
         <v>1</v>
@@ -18858,99 +18858,99 @@
         <v>1</v>
       </c>
       <c r="AP112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ112" t="n">
         <v>1</v>
       </c>
       <c r="AR112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT112" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU112" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AV112" t="n">
         <v>0</v>
       </c>
       <c r="AW112" t="n">
-        <v>19</v>
+        <v>8</v>
       </c>
       <c r="AX112" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY112" t="n">
-        <v>5.901101922244729</v>
+        <v>4.388355132131548</v>
       </c>
       <c r="AZ112" t="n">
-        <v>-0.9011019222447292</v>
+        <v>-0.3883551321315482</v>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>PGE</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B113" t="n">
-        <v>0.7080605644597759</v>
+        <v>0.4407467228894335</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Aprimorado</t>
+          <t>Intermediário</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>0.6979978763983506</v>
+        <v>0.4331568546537495</v>
       </c>
       <c r="E113" t="n">
-        <v>1</v>
+        <v>0.4480724791053855</v>
       </c>
       <c r="F113" t="n">
-        <v>0.7239640169365842</v>
+        <v>0.2392146296411173</v>
       </c>
       <c r="G113" t="n">
-        <v>0.4726402015595599</v>
+        <v>0.6738474634857513</v>
       </c>
       <c r="H113" t="n">
-        <v>0.774131913621328</v>
+        <v>0.715498338063645</v>
       </c>
       <c r="I113" t="n">
         <v>0.5</v>
       </c>
       <c r="J113" t="n">
-        <v>0.4416666666666667</v>
+        <v>0.3250000000000001</v>
       </c>
       <c r="K113" t="n">
-        <v>0.4870785579360365</v>
+        <v>0.3198595250632113</v>
       </c>
       <c r="L113" t="n">
-        <v>0.8957216940728419</v>
+        <v>0.3382302099500095</v>
       </c>
       <c r="M113" t="n">
-        <v>0.7172638476075258</v>
+        <v>0.4476883776441789</v>
       </c>
       <c r="N113" t="inlineStr">
         <is>
-          <t>PGE</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="O113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="P113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q113" t="n">
         <v>1</v>
       </c>
       <c r="R113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S113" t="n">
         <v>1</v>
@@ -18962,13 +18962,13 @@
         <v>1</v>
       </c>
       <c r="V113" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="W113" t="n">
         <v>0</v>
       </c>
       <c r="X113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y113" t="n">
         <v>0</v>
@@ -18977,34 +18977,34 @@
         <v>1</v>
       </c>
       <c r="AA113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB113" t="n">
         <v>0</v>
       </c>
       <c r="AC113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE113" t="n">
         <v>0</v>
       </c>
       <c r="AF113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AG113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH113" t="n">
         <v>0</v>
       </c>
       <c r="AI113" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK113" t="n">
         <v>1</v>
@@ -19028,87 +19028,87 @@
         <v>1</v>
       </c>
       <c r="AR113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT113" t="n">
         <v>1</v>
       </c>
       <c r="AU113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AV113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW113" t="n">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="AX113" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY113" t="n">
-        <v>4.450890498873667</v>
+        <v>4.97130613733782</v>
       </c>
       <c r="AZ113" t="n">
-        <v>-0.4508904988736671</v>
+        <v>1.02869386266218</v>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>CAMPOS DOS GOYTACAZES</t>
         </is>
       </c>
       <c r="B114" t="n">
-        <v>0.4407467228894335</v>
+        <v>0.06697490117631651</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Intermediário</t>
+          <t>Inexpressivo</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>0.4331568546537495</v>
+        <v>0.0577226288678418</v>
       </c>
       <c r="E114" t="n">
-        <v>0.4480724791053855</v>
+        <v>0</v>
       </c>
       <c r="F114" t="n">
-        <v>0.2392146296411173</v>
+        <v>0.0772395956339562</v>
       </c>
       <c r="G114" t="n">
-        <v>0.6738474634857513</v>
+        <v>0.09726582531093959</v>
       </c>
       <c r="H114" t="n">
-        <v>0.715498338063645</v>
+        <v>0.1028279330765613</v>
       </c>
       <c r="I114" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J114" t="n">
-        <v>0.3250000000000001</v>
+        <v>0.1249999999999999</v>
       </c>
       <c r="K114" t="n">
-        <v>0.3198595250632113</v>
+        <v>0.09544694339318134</v>
       </c>
       <c r="L114" t="n">
-        <v>0.3382302099500095</v>
+        <v>0.0736082159485815</v>
       </c>
       <c r="M114" t="n">
-        <v>0.4476883776441789</v>
+        <v>0.07543698221223774</v>
       </c>
       <c r="N114" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>CAMPOS DOS GOYTACAZES</t>
         </is>
       </c>
       <c r="O114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="P114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q114" t="n">
         <v>1</v>
@@ -19126,13 +19126,13 @@
         <v>1</v>
       </c>
       <c r="V114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="W114" t="n">
         <v>0</v>
       </c>
       <c r="X114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y114" t="n">
         <v>0</v>
@@ -19153,7 +19153,7 @@
         <v>1</v>
       </c>
       <c r="AE114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF114" t="n">
         <v>1</v>
@@ -19165,10 +19165,10 @@
         <v>0</v>
       </c>
       <c r="AI114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK114" t="n">
         <v>1</v>
@@ -19186,7 +19186,7 @@
         <v>1</v>
       </c>
       <c r="AP114" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ114" t="n">
         <v>1</v>
@@ -19198,189 +19198,25 @@
         <v>1</v>
       </c>
       <c r="AT114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU114" t="n">
         <v>1</v>
       </c>
       <c r="AV114" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW114" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AX114" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AY114" t="n">
-        <v>5.006948750922162</v>
+        <v>5.786417909722805</v>
       </c>
       <c r="AZ114" t="n">
-        <v>0.9930512490778378</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>CAMPOS DOS GOYTACAZES</t>
-        </is>
-      </c>
-      <c r="B115" t="n">
-        <v>0.06697490117631651</v>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Inexpressivo</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>0.0577226288678418</v>
-      </c>
-      <c r="E115" t="n">
-        <v>0</v>
-      </c>
-      <c r="F115" t="n">
-        <v>0.0772395956339562</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0.09726582531093959</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.1028279330765613</v>
-      </c>
-      <c r="I115" t="n">
-        <v>0</v>
-      </c>
-      <c r="J115" t="n">
-        <v>0.1249999999999999</v>
-      </c>
-      <c r="K115" t="n">
-        <v>0.09544694339318134</v>
-      </c>
-      <c r="L115" t="n">
-        <v>0.0736082159485815</v>
-      </c>
-      <c r="M115" t="n">
-        <v>0.07543698221223774</v>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>CAMPOS DOS GOYTACAZES</t>
-        </is>
-      </c>
-      <c r="O115" t="n">
-        <v>5</v>
-      </c>
-      <c r="P115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q115" t="n">
-        <v>1</v>
-      </c>
-      <c r="R115" t="n">
-        <v>1</v>
-      </c>
-      <c r="S115" t="n">
-        <v>1</v>
-      </c>
-      <c r="T115" t="n">
-        <v>1</v>
-      </c>
-      <c r="U115" t="n">
-        <v>1</v>
-      </c>
-      <c r="V115" t="n">
-        <v>17</v>
-      </c>
-      <c r="W115" t="n">
-        <v>0</v>
-      </c>
-      <c r="X115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Y115" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AA115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AB115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AD115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AE115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AF115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AG115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AH115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AJ115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AK115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AL115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AM115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AO115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AP115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AQ115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AR115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AS115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AT115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AU115" t="n">
-        <v>1</v>
-      </c>
-      <c r="AV115" t="n">
-        <v>0</v>
-      </c>
-      <c r="AW115" t="n">
-        <v>17</v>
-      </c>
-      <c r="AX115" t="n">
-        <v>5</v>
-      </c>
-      <c r="AY115" t="n">
-        <v>5.784457706784014</v>
-      </c>
-      <c r="AZ115" t="n">
-        <v>-0.7844577067840142</v>
+        <v>-0.7864179097228048</v>
       </c>
     </row>
   </sheetData>
@@ -19500,7 +19336,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -19817,10 +19653,10 @@
         <v>3</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.556869805656601</v>
+        <v>4.499459936695778</v>
       </c>
       <c r="AZ2" t="n">
-        <v>-1.556869805656601</v>
+        <v>-1.499459936695778</v>
       </c>
     </row>
     <row r="3">
@@ -19981,10 +19817,10 @@
         <v>4</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.984703813417788</v>
+        <v>4.947985363603857</v>
       </c>
       <c r="AZ3" t="n">
-        <v>-0.9847038134177879</v>
+        <v>-0.9479853636038573</v>
       </c>
     </row>
     <row r="4">
@@ -20145,10 +19981,10 @@
         <v>5</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.914480298210121</v>
+        <v>5.922728808971473</v>
       </c>
       <c r="AZ4" t="n">
-        <v>-0.9144802982101208</v>
+        <v>-0.9227288089714731</v>
       </c>
     </row>
     <row r="5">
@@ -20309,10 +20145,10 @@
         <v>5</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.901101922244729</v>
+        <v>5.908703412012933</v>
       </c>
       <c r="AZ5" t="n">
-        <v>-0.9011019222447292</v>
+        <v>-0.9087034120129331</v>
       </c>
     </row>
     <row r="6">
@@ -20473,10 +20309,10 @@
         <v>5</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.855441571812216</v>
+        <v>5.860834781191169</v>
       </c>
       <c r="AZ6" t="n">
-        <v>-0.8554415718122161</v>
+        <v>-0.8608347811911692</v>
       </c>
     </row>
     <row r="7">
@@ -20637,10 +20473,10 @@
         <v>5</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.84654505636323</v>
+        <v>5.851508001838982</v>
       </c>
       <c r="AZ7" t="n">
-        <v>-0.8465450563632304</v>
+        <v>-0.8515080018389822</v>
       </c>
     </row>
     <row r="8">
@@ -20801,10 +20637,10 @@
         <v>5</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.820388161009607</v>
+        <v>5.824086075479116</v>
       </c>
       <c r="AZ8" t="n">
-        <v>-0.8203881610096069</v>
+        <v>-0.8240860754791157</v>
       </c>
     </row>
     <row r="9">
@@ -20965,10 +20801,10 @@
         <v>5</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.791158423586658</v>
+        <v>5.79344269459258</v>
       </c>
       <c r="AZ9" t="n">
-        <v>-0.7911584235866584</v>
+        <v>-0.7934426945925797</v>
       </c>
     </row>
     <row r="10">
@@ -21129,10 +20965,10 @@
         <v>5</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.784457706784014</v>
+        <v>5.786417909722805</v>
       </c>
       <c r="AZ10" t="n">
-        <v>-0.7844577067840142</v>
+        <v>-0.7864179097228048</v>
       </c>
     </row>
     <row r="11">
@@ -21293,10 +21129,10 @@
         <v>5</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.779083900567769</v>
+        <v>5.780784209073631</v>
       </c>
       <c r="AZ11" t="n">
-        <v>-0.7790839005677688</v>
+        <v>-0.780784209073631</v>
       </c>
     </row>
     <row r="12">
@@ -21457,10 +21293,10 @@
         <v>5</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.762839611227163</v>
+        <v>5.763754294015123</v>
       </c>
       <c r="AZ12" t="n">
-        <v>-0.7628396112271627</v>
+        <v>-0.763754294015123</v>
       </c>
     </row>
     <row r="13">
@@ -21621,10 +21457,10 @@
         <v>5</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.754925078418034</v>
+        <v>5.755456989119777</v>
       </c>
       <c r="AZ13" t="n">
-        <v>-0.7549250784180339</v>
+        <v>-0.7554569891197769</v>
       </c>
     </row>
   </sheetData>
@@ -21690,19 +21526,19 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>-0.3406981589555891</v>
+        <v>-0.3536391884536563</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00020793187152278</v>
+        <v>0.000121853958298964</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5635900506657059</v>
+        <v>-0.5840323353444042</v>
       </c>
       <c r="F2" t="n">
-        <v>6.645751402114432e-11</v>
+        <v>1.120567132136756e-11</v>
       </c>
       <c r="G2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3">
@@ -21717,19 +21553,19 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>-0.3396515221417354</v>
+        <v>-0.3515396185719185</v>
       </c>
       <c r="D3" t="n">
-        <v>0.0002181148851452681</v>
+        <v>0.0001345520916386484</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5262873174729016</v>
+        <v>-0.5436404627671312</v>
       </c>
       <c r="F3" t="n">
-        <v>1.812058471204874e-09</v>
+        <v>4.899102675543491e-10</v>
       </c>
       <c r="G3" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="4">
@@ -21744,19 +21580,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>-0.3054342728649688</v>
+        <v>-0.3172059802301452</v>
       </c>
       <c r="D4" t="n">
-        <v>0.0009513121704136199</v>
+        <v>0.0006186422813291948</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5369688885750871</v>
+        <v>-0.5565299502016301</v>
       </c>
       <c r="F4" t="n">
-        <v>7.326174102928061e-10</v>
+        <v>1.550009186263361e-10</v>
       </c>
       <c r="G4" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="5">
@@ -21771,19 +21607,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>-0.2624295047028513</v>
+        <v>-0.2688972402835912</v>
       </c>
       <c r="D5" t="n">
-        <v>0.004791663078326048</v>
+        <v>0.003978326070688832</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.4242113878188745</v>
+        <v>-0.4303240552250091</v>
       </c>
       <c r="F5" t="n">
-        <v>2.55718931233636e-06</v>
+        <v>1.963025904223017e-06</v>
       </c>
       <c r="G5" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6">
@@ -21798,19 +21634,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>-0.2398493548115866</v>
+        <v>-0.2530998418570135</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01016100373319056</v>
+        <v>0.006835348563140036</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.399920630554302</v>
+        <v>-0.423969279286774</v>
       </c>
       <c r="F6" t="n">
-        <v>1.041673265296663e-05</v>
+        <v>2.876837115799903e-06</v>
       </c>
       <c r="G6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="7">
@@ -21825,19 +21661,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>-0.1659244682656085</v>
+        <v>-0.1767829295386024</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0776788304967046</v>
+        <v>0.06105248074742115</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.2963710385007829</v>
+        <v>-0.3098400695959679</v>
       </c>
       <c r="F7" t="n">
-        <v>0.00136593058720034</v>
+        <v>0.0008389775690197738</v>
       </c>
       <c r="G7" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="8">
@@ -21852,19 +21688,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>-0.2784465270242457</v>
+        <v>-0.2858314766725868</v>
       </c>
       <c r="D8" t="n">
-        <v>0.002701632314674399</v>
+        <v>0.002148193065546599</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.3672125149422659</v>
+        <v>-0.3745065563343369</v>
       </c>
       <c r="F8" t="n">
-        <v>5.847422255748719e-05</v>
+        <v>4.378465491002758e-05</v>
       </c>
       <c r="G8" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="9">
@@ -21879,19 +21715,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>-0.2784400972211661</v>
+        <v>-0.2888256977382798</v>
       </c>
       <c r="D9" t="n">
-        <v>0.002702272246353499</v>
+        <v>0.001918781368349107</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.4551967977658341</v>
+        <v>-0.4712086589955946</v>
       </c>
       <c r="F9" t="n">
-        <v>3.611308156368822e-07</v>
+        <v>1.382676760234548e-07</v>
       </c>
       <c r="G9" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="10">
@@ -21906,19 +21742,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>-0.408652911348399</v>
+        <v>-0.4217130521676901</v>
       </c>
       <c r="D10" t="n">
-        <v>6.366652404123621e-06</v>
+        <v>3.288839975450775e-06</v>
       </c>
       <c r="E10" t="n">
-        <v>-0.6024472506253147</v>
+        <v>-0.6172039156635458</v>
       </c>
       <c r="F10" t="n">
-        <v>1.330415648494321e-12</v>
+        <v>3.334058916279358e-13</v>
       </c>
       <c r="G10" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="11">
@@ -21933,19 +21769,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>-0.2208182320144662</v>
+        <v>-0.2181702425601326</v>
       </c>
       <c r="D11" t="n">
-        <v>0.01822905522052611</v>
+        <v>0.02026344262460584</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.3110714011924727</v>
+        <v>-0.3087067840751326</v>
       </c>
       <c r="F11" t="n">
-        <v>0.0007551980674631738</v>
+        <v>0.0008786356665689623</v>
       </c>
       <c r="G11" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="12">
@@ -21960,19 +21796,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>-0.2210243462671591</v>
+        <v>-0.228511679446386</v>
       </c>
       <c r="D12" t="n">
-        <v>0.01811826962403107</v>
+        <v>0.01491626261161617</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.4479348207935061</v>
+        <v>-0.4549210536163399</v>
       </c>
       <c r="F12" t="n">
-        <v>5.81429389239123e-07</v>
+        <v>4.147469965288173e-07</v>
       </c>
       <c r="G12" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="13">
@@ -21987,19 +21823,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>-0.5858628855267625</v>
+        <v>-0.6142224792518278</v>
       </c>
       <c r="D13" t="n">
-        <v>7.524928663039443e-12</v>
+        <v>4.650615952194998e-13</v>
       </c>
       <c r="E13" t="n">
-        <v>-0.7701216222937013</v>
+        <v>-0.7985684917771273</v>
       </c>
       <c r="F13" t="n">
-        <v>1.316118433785414e-23</v>
+        <v>3.172119247801632e-26</v>
       </c>
       <c r="G13" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="14">
@@ -22014,19 +21850,19 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>-0.6316341391916859</v>
+        <v>-0.6598278267519398</v>
       </c>
       <c r="D14" t="n">
-        <v>4.884866242857068e-14</v>
+        <v>1.891471317162023e-15</v>
       </c>
       <c r="E14" t="n">
-        <v>-0.7822688761310098</v>
+        <v>-0.8074426422669804</v>
       </c>
       <c r="F14" t="n">
-        <v>9.092245571323009e-25</v>
+        <v>3.383202107354667e-27</v>
       </c>
       <c r="G14" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="15">
@@ -22041,19 +21877,19 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>-0.4206259304425755</v>
+        <v>-0.4435051454294432</v>
       </c>
       <c r="D15" t="n">
-        <v>3.168210310075213e-06</v>
+        <v>8.663886975460214e-07</v>
       </c>
       <c r="E15" t="n">
-        <v>-0.669612607541883</v>
+        <v>-0.6956948191547062</v>
       </c>
       <c r="F15" t="n">
-        <v>3.782364498155078e-16</v>
+        <v>1.21434044624998e-17</v>
       </c>
       <c r="G15" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="16">
@@ -22068,19 +21904,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>-0.6015336405376018</v>
+        <v>-0.6180644615796289</v>
       </c>
       <c r="D16" t="n">
-        <v>1.467483609708662e-12</v>
+        <v>3.026706493670625e-13</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.7479081113756942</v>
+        <v>-0.7578916596932108</v>
       </c>
       <c r="F16" t="n">
-        <v>1.169229946329538e-21</v>
+        <v>2.543858701822587e-22</v>
       </c>
       <c r="G16" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="17">
@@ -22095,19 +21931,19 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>-0.4179836333857374</v>
+        <v>-0.4450157688169389</v>
       </c>
       <c r="D17" t="n">
-        <v>3.704313276246543e-06</v>
+        <v>7.871224573420123e-07</v>
       </c>
       <c r="E17" t="n">
-        <v>-0.5988035336338049</v>
+        <v>-0.6330055310917934</v>
       </c>
       <c r="F17" t="n">
-        <v>1.96349415999893e-12</v>
+        <v>5.379455649997074e-14</v>
       </c>
       <c r="G17" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="18">
@@ -22122,19 +21958,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>-0.4315079517120941</v>
+        <v>-0.4551261022478227</v>
       </c>
       <c r="D18" t="n">
-        <v>1.640869624460024e-06</v>
+        <v>4.091945398924727e-07</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5865062201288765</v>
+        <v>-0.607524842981976</v>
       </c>
       <c r="F18" t="n">
-        <v>7.048597403049404e-12</v>
+        <v>9.698879829303474e-13</v>
       </c>
       <c r="G18" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="19">
@@ -22149,19 +21985,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>-0.5215943160571945</v>
+        <v>-0.539746285183729</v>
       </c>
       <c r="D19" t="n">
-        <v>2.671138606420977e-09</v>
+        <v>6.870511760661433e-10</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.5561125554328342</v>
+        <v>-0.5669131509419628</v>
       </c>
       <c r="F19" t="n">
-        <v>1.332420378551924e-10</v>
+        <v>5.914477087529541e-11</v>
       </c>
       <c r="G19" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="20">
@@ -22176,19 +22012,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>-0.4247355054535192</v>
+        <v>-0.4473463946199044</v>
       </c>
       <c r="D20" t="n">
-        <v>2.477828076853927e-06</v>
+        <v>6.781997244513826e-07</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.5712283920884667</v>
+        <v>-0.5927111434413707</v>
       </c>
       <c r="F20" t="n">
-        <v>3.206766082395448e-11</v>
+        <v>4.643221797923806e-12</v>
       </c>
       <c r="G20" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="21">
@@ -22203,19 +22039,19 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>-0.4291676736790264</v>
+        <v>-0.4527736366583363</v>
       </c>
       <c r="D21" t="n">
-        <v>1.893940884146586e-06</v>
+        <v>4.773704400842837e-07</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.6719385290492191</v>
+        <v>-0.6910674120370101</v>
       </c>
       <c r="F21" t="n">
-        <v>2.743778308709704e-16</v>
+        <v>2.426826811871227e-17</v>
       </c>
       <c r="G21" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="22">
@@ -22230,19 +22066,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>-0.3733104079817465</v>
+        <v>-0.3705473266921182</v>
       </c>
       <c r="D22" t="n">
-        <v>4.298075941331022e-05</v>
+        <v>5.345934095125833e-05</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.4091164769727573</v>
+        <v>-0.4066945589437259</v>
       </c>
       <c r="F22" t="n">
-        <v>6.19999577488426e-06</v>
+        <v>7.824303835304428e-06</v>
       </c>
       <c r="G22" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="23">
@@ -22257,19 +22093,19 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>-0.4528679662903856</v>
+        <v>-0.4729684445564815</v>
       </c>
       <c r="D23" t="n">
-        <v>4.212258283016884e-07</v>
+        <v>1.223714213656e-07</v>
       </c>
       <c r="E23" t="n">
-        <v>-0.5804055616484125</v>
+        <v>-0.5904092304713459</v>
       </c>
       <c r="F23" t="n">
-        <v>1.302950283121927e-11</v>
+        <v>5.880475496746782e-12</v>
       </c>
       <c r="G23" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
   </sheetData>
@@ -22325,19 +22161,19 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
-        <v>-0.3406981589555891</v>
+        <v>-0.3536391884536563</v>
       </c>
       <c r="D2" t="n">
-        <v>0.00020793187152278</v>
+        <v>0.000121853958298964</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.5858628855267625</v>
+        <v>-0.6142224792518278</v>
       </c>
       <c r="F2" t="n">
-        <v>7.524928663039443e-12</v>
+        <v>4.650615952194998e-13</v>
       </c>
     </row>
     <row r="3">
@@ -22347,19 +22183,19 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C3" t="n">
-        <v>-0.3082625520944138</v>
+        <v>-0.3216077458223461</v>
       </c>
       <c r="D3" t="n">
-        <v>0.001110012200095294</v>
+        <v>0.0006888168773392441</v>
       </c>
       <c r="E3" t="n">
-        <v>-0.5751205444588066</v>
+        <v>-0.6044401696841127</v>
       </c>
       <c r="F3" t="n">
-        <v>6.127101624114373e-11</v>
+        <v>4.310945692333639e-12</v>
       </c>
     </row>
     <row r="4">
@@ -22369,19 +22205,19 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C4" t="n">
-        <v>-0.3717515309009851</v>
+        <v>-0.3927371372949901</v>
       </c>
       <c r="D4" t="n">
-        <v>0.001531316623980648</v>
+        <v>0.0008440697408196652</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.6260347446093832</v>
+        <v>-0.6738924045060105</v>
       </c>
       <c r="F4" t="n">
-        <v>6.807852992601752e-09</v>
+        <v>2.207417405163206e-10</v>
       </c>
     </row>
     <row r="5">
@@ -22391,19 +22227,19 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C5" t="n">
-        <v>-0.2981219334338425</v>
+        <v>-0.3150554486438921</v>
       </c>
       <c r="D5" t="n">
-        <v>0.005585606770674525</v>
+        <v>0.003511664129071357</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.5697065574589745</v>
+        <v>-0.6082599494465897</v>
       </c>
       <c r="F5" t="n">
-        <v>1.26789073747171e-08</v>
+        <v>8.408843251174347e-10</v>
       </c>
     </row>
     <row r="6">
@@ -22416,16 +22252,16 @@
         <v>57</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.324312458900742</v>
+        <v>-0.3636597142259088</v>
       </c>
       <c r="D6" t="n">
-        <v>0.01384803003517116</v>
+        <v>0.005425135891464239</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.567866591219807</v>
+        <v>-0.6272745300579919</v>
       </c>
       <c r="F6" t="n">
-        <v>4.085467867541814e-06</v>
+        <v>1.77678775797738e-07</v>
       </c>
     </row>
   </sheetData>
@@ -22603,7 +22439,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C5" t="n">
         <v>0.2386495114889209</v>
@@ -22612,22 +22448,22 @@
         <v>0.7766696831301108</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4342107210089083</v>
+        <v>0.4319675122498484</v>
       </c>
       <c r="F5" t="n">
-        <v>5.137931034482759</v>
+        <v>5.107142857142857</v>
       </c>
       <c r="G5" t="n">
-        <v>15.20689655172414</v>
+        <v>14.96428571428571</v>
       </c>
       <c r="H5" t="n">
-        <v>16</v>
+        <v>15.5</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7241379310344828</v>
+        <v>0.7142857142857143</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03448275862068965</v>
+        <v>0.03571428571428571</v>
       </c>
     </row>
   </sheetData>
@@ -22760,10 +22596,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="C4" t="n">
-        <v>0.5123950765963174</v>
+        <v>0.5141033555222874</v>
       </c>
       <c r="D4" t="n">
         <v>0.4338685236850021</v>
@@ -22772,16 +22608,16 @@
         <v>0.6571649299064324</v>
       </c>
       <c r="F4" t="n">
-        <v>4.9</v>
+        <v>4.777777777777778</v>
       </c>
       <c r="G4" t="n">
-        <v>15.8</v>
+        <v>15.11111111111111</v>
       </c>
       <c r="H4" t="n">
-        <v>0.4</v>
+        <v>0.3333333333333333</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6</v>
+        <v>0.5555555555555556</v>
       </c>
     </row>
     <row r="5">
@@ -22893,28 +22729,28 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="D2" t="n">
         <v>42</v>
       </c>
       <c r="E2" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="F2" t="n">
-        <v>0.1579573965911467</v>
+        <v>0.1531818589901404</v>
       </c>
       <c r="G2" t="n">
         <v>0.2363924362170083</v>
       </c>
       <c r="H2" t="n">
-        <v>0.0784350396258616</v>
+        <v>0.08321057722686781</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.2144087686880307</v>
+        <v>-0.2300417273144235</v>
       </c>
       <c r="J2" t="n">
-        <v>0.02197852896945058</v>
+        <v>0.01423982770695042</v>
       </c>
     </row>
     <row r="3">
@@ -22929,28 +22765,28 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" t="n">
         <v>6</v>
       </c>
       <c r="E3" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="F3" t="n">
-        <v>0.1604105858831046</v>
+        <v>0.1572646982160066</v>
       </c>
       <c r="G3" t="n">
         <v>0.6628452667169353</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5024346808338308</v>
+        <v>0.5055805685009287</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.635782604572395</v>
+        <v>-0.648533110442986</v>
       </c>
       <c r="J3" t="n">
-        <v>2.967814993184355e-14</v>
+        <v>8.067323291181628e-15</v>
       </c>
     </row>
     <row r="4">
@@ -22965,28 +22801,28 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D4" t="n">
         <v>4</v>
       </c>
       <c r="E4" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9646017699115044</v>
       </c>
       <c r="F4" t="n">
-        <v>0.168876957636691</v>
+        <v>0.1658664658144351</v>
       </c>
       <c r="G4" t="n">
         <v>0.6812373839102225</v>
       </c>
       <c r="H4" t="n">
-        <v>0.5123604262735315</v>
+        <v>0.5153709180957874</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5342486649791074</v>
+        <v>-0.5448004007598877</v>
       </c>
       <c r="J4" t="n">
-        <v>9.254200292273766e-10</v>
+        <v>4.425929410891735e-10</v>
       </c>
     </row>
     <row r="5">
@@ -23001,7 +22837,7 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
@@ -23010,7 +22846,7 @@
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1868545164533062</v>
+        <v>0.184109684154109</v>
       </c>
       <c r="G5" t="inlineStr"/>
       <c r="H5" t="inlineStr"/>
@@ -23029,7 +22865,7 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
@@ -23038,7 +22874,7 @@
         <v>1</v>
       </c>
       <c r="F6" t="n">
-        <v>0.1868545164533062</v>
+        <v>0.184109684154109</v>
       </c>
       <c r="G6" t="inlineStr"/>
       <c r="H6" t="inlineStr"/>
@@ -23048,37 +22884,37 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="C7" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D7" t="n">
         <v>1</v>
       </c>
       <c r="E7" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="F7" t="n">
-        <v>0.1826929357112753</v>
+        <v>0.1798864390099244</v>
       </c>
       <c r="G7" t="n">
         <v>0.6571131403027882</v>
       </c>
       <c r="H7" t="n">
-        <v>0.4744202045915129</v>
+        <v>0.4772267012928638</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.250693992717326</v>
+        <v>-0.2556866257402417</v>
       </c>
       <c r="J7" t="n">
-        <v>0.007139124327399933</v>
+        <v>0.006269243504490489</v>
       </c>
     </row>
   </sheetData>
@@ -23134,10 +22970,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D2" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
@@ -23157,10 +22993,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D3" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
@@ -23180,10 +23016,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
@@ -23203,10 +23039,10 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
@@ -23226,10 +23062,10 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.9734513274336283</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
@@ -23249,10 +23085,10 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D7" t="n">
-        <v>0.956140350877193</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
@@ -23272,10 +23108,10 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D8" t="n">
-        <v>0.956140350877193</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
@@ -23295,10 +23131,10 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D9" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
@@ -23318,10 +23154,10 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D10" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
@@ -23341,10 +23177,10 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D11" t="n">
-        <v>0.9385964912280702</v>
+        <v>0.9380530973451328</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
@@ -23364,10 +23200,10 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D12" t="n">
-        <v>0.9210526315789473</v>
+        <v>0.9203539823008849</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
@@ -23387,10 +23223,10 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D13" t="n">
-        <v>0.8947368421052632</v>
+        <v>0.8938053097345132</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
@@ -23410,10 +23246,10 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="D14" t="n">
-        <v>0.8771929824561403</v>
+        <v>0.8761061946902655</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
@@ -23433,10 +23269,10 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="D15" t="n">
-        <v>0.8245614035087719</v>
+        <v>0.8230088495575221</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
@@ -23456,10 +23292,10 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D16" t="n">
-        <v>0.7894736842105263</v>
+        <v>0.7876106194690266</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
@@ -23479,10 +23315,10 @@
         </is>
       </c>
       <c r="C17" t="n">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D17" t="n">
-        <v>0.7719298245614035</v>
+        <v>0.7699115044247787</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
@@ -23502,10 +23338,10 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D18" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7610619469026548</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
@@ -23525,10 +23361,10 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D19" t="n">
-        <v>0.7631578947368421</v>
+        <v>0.7610619469026548</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
@@ -23548,10 +23384,10 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="D20" t="n">
-        <v>0.6578947368421053</v>
+        <v>0.6548672566371682</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
@@ -23571,10 +23407,10 @@
         </is>
       </c>
       <c r="C21" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D21" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.5221238938053098</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
@@ -23597,7 +23433,7 @@
         <v>58</v>
       </c>
       <c r="D22" t="n">
-        <v>0.5087719298245614</v>
+        <v>0.5132743362831859</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
@@ -23617,10 +23453,10 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="D23" t="n">
-        <v>0.4035087719298245</v>
+        <v>0.3982300884955752</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
@@ -23643,7 +23479,7 @@
         <v>23</v>
       </c>
       <c r="D24" t="n">
-        <v>0.2017543859649123</v>
+        <v>0.2035398230088496</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
@@ -23666,7 +23502,7 @@
         <v>22</v>
       </c>
       <c r="D25" t="n">
-        <v>0.1929824561403509</v>
+        <v>0.1946902654867257</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
@@ -23689,7 +23525,7 @@
         <v>17</v>
       </c>
       <c r="D26" t="n">
-        <v>0.1491228070175439</v>
+        <v>0.1504424778761062</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
@@ -23709,10 +23545,10 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="D27" t="n">
-        <v>0.05263157894736842</v>
+        <v>0.04424778761061947</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
@@ -23768,7 +23604,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C2" t="n">
         <v>1</v>
@@ -23791,10 +23627,10 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C3" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -23803,7 +23639,7 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23814,10 +23650,10 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C4" t="n">
-        <v>0.9912280701754386</v>
+        <v>0.9911504424778761</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -23826,7 +23662,7 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23837,10 +23673,10 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C5" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9646017699115044</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -23860,10 +23696,10 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C6" t="n">
-        <v>0.9649122807017544</v>
+        <v>0.9646017699115044</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -23883,10 +23719,10 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C7" t="n">
-        <v>0.956140350877193</v>
+        <v>0.9557522123893806</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -23895,7 +23731,7 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23906,10 +23742,10 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C8" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -23929,10 +23765,10 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C9" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -23952,10 +23788,10 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="C10" t="n">
-        <v>0.9473684210526315</v>
+        <v>0.9469026548672567</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -23964,7 +23800,7 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -23975,10 +23811,10 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="C11" t="n">
-        <v>0.9298245614035088</v>
+        <v>0.9292035398230089</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -23998,10 +23834,10 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C12" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -24021,10 +23857,10 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C13" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -24044,10 +23880,10 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="C14" t="n">
-        <v>0.631578947368421</v>
+        <v>0.6283185840707964</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -24056,7 +23892,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Achado 6 - Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>Achado 6 - Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
     </row>
@@ -24067,10 +23903,10 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C15" t="n">
-        <v>0.6140350877192983</v>
+        <v>0.6106194690265486</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -24090,10 +23926,10 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="C16" t="n">
-        <v>0.6140350877192983</v>
+        <v>0.6106194690265486</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -24223,7 +24059,7 @@
       </c>
       <c r="U1" t="inlineStr">
         <is>
-          <t>6. Contratações de TIC sem governança técnica e controle de resultados</t>
+          <t>6. Fragilidades na governança técnica da fase preparatória das contratações de TIC</t>
         </is>
       </c>
       <c r="V1" t="inlineStr">
@@ -24385,11 +24221,11 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>IASERJ</t>
+          <t>CEASA</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.4970205662625881</v>
+        <v>0.4565981967508033</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -24397,7 +24233,7 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.5</v>
+        <v>0.4462407473352393</v>
       </c>
       <c r="E2" t="n">
         <v>0.5</v>
@@ -24421,14 +24257,14 @@
         <v>0.4686802611500751</v>
       </c>
       <c r="L2" t="n">
-        <v>0.4999999999999994</v>
+        <v>0.3217525038800234</v>
       </c>
       <c r="M2" t="n">
-        <v>0.4942955913713882</v>
+        <v>0.4660710671287835</v>
       </c>
       <c r="N2" t="inlineStr">
         <is>
-          <t>IASERJ</t>
+          <t>CEASA</t>
         </is>
       </c>
       <c r="O2" t="n">
@@ -24453,16 +24289,16 @@
         <v>1</v>
       </c>
       <c r="V2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="W2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="X2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y2" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z2" t="n">
         <v>1</v>
@@ -24534,26 +24370,26 @@
         <v>1</v>
       </c>
       <c r="AW2" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AX2" t="n">
         <v>6</v>
       </c>
       <c r="AY2" t="n">
-        <v>4.889889586315107</v>
+        <v>4.936737659449798</v>
       </c>
       <c r="AZ2" t="n">
-        <v>1.110110413684893</v>
+        <v>1.063262340550202</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>CEASA</t>
+          <t>TERESÓPOLIS</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.4565981967508033</v>
+        <v>0.4415724015178892</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -24561,38 +24397,38 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.4462407473352393</v>
+        <v>0.5587955805379498</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="F3" t="n">
-        <v>0.5</v>
+        <v>0.07031539117323786</v>
       </c>
       <c r="G3" t="n">
-        <v>0.5</v>
+        <v>0.7319346119972763</v>
       </c>
       <c r="H3" t="n">
-        <v>0.5</v>
+        <v>0.7644078595454109</v>
       </c>
       <c r="I3" t="n">
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.4166666666666665</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="K3" t="n">
-        <v>0.4686802611500751</v>
+        <v>0.3159739202007785</v>
       </c>
       <c r="L3" t="n">
-        <v>0.3217525038800234</v>
+        <v>0.1499999999999999</v>
       </c>
       <c r="M3" t="n">
-        <v>0.4660710671287835</v>
+        <v>0.3343606802148462</v>
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>CEASA</t>
+          <t>TERESÓPOLIS</t>
         </is>
       </c>
       <c r="O3" t="n">
@@ -24617,7 +24453,7 @@
         <v>1</v>
       </c>
       <c r="V3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="W3" t="n">
         <v>0</v>
@@ -24626,13 +24462,13 @@
         <v>1</v>
       </c>
       <c r="Y3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z3" t="n">
         <v>1</v>
       </c>
       <c r="AA3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB3" t="n">
         <v>0</v>
@@ -24653,7 +24489,7 @@
         <v>1</v>
       </c>
       <c r="AH3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI3" t="n">
         <v>1</v>
@@ -24695,29 +24531,29 @@
         <v>1</v>
       </c>
       <c r="AV3" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW3" t="n">
-        <v>23</v>
+        <v>19</v>
       </c>
       <c r="AX3" t="n">
         <v>6</v>
       </c>
       <c r="AY3" t="n">
-        <v>4.973974989458986</v>
+        <v>4.969505519069765</v>
       </c>
       <c r="AZ3" t="n">
-        <v>1.026025010541014</v>
+        <v>1.030494480930235</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>TERESÓPOLIS</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.4415724015178892</v>
+        <v>0.4407467228894335</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -24725,38 +24561,38 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.5587955805379498</v>
+        <v>0.4331568546537495</v>
       </c>
       <c r="E4" t="n">
-        <v>0</v>
+        <v>0.4480724791053855</v>
       </c>
       <c r="F4" t="n">
-        <v>0.07031539117323786</v>
+        <v>0.2392146296411173</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7319346119972763</v>
+        <v>0.6738474634857513</v>
       </c>
       <c r="H4" t="n">
-        <v>0.7644078595454109</v>
+        <v>0.715498338063645</v>
       </c>
       <c r="I4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J4" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.3250000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.3159739202007785</v>
+        <v>0.3198595250632113</v>
       </c>
       <c r="L4" t="n">
-        <v>0.1499999999999999</v>
+        <v>0.3382302099500095</v>
       </c>
       <c r="M4" t="n">
-        <v>0.3343606802148462</v>
+        <v>0.4476883776441789</v>
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>TERESÓPOLIS</t>
+          <t>ISP</t>
         </is>
       </c>
       <c r="O4" t="n">
@@ -24781,7 +24617,7 @@
         <v>1</v>
       </c>
       <c r="V4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
@@ -24796,7 +24632,7 @@
         <v>1</v>
       </c>
       <c r="AA4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB4" t="n">
         <v>0</v>
@@ -24808,7 +24644,7 @@
         <v>1</v>
       </c>
       <c r="AE4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF4" t="n">
         <v>1</v>
@@ -24820,7 +24656,7 @@
         <v>0</v>
       </c>
       <c r="AI4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AJ4" t="n">
         <v>1</v>
@@ -24841,7 +24677,7 @@
         <v>1</v>
       </c>
       <c r="AP4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AQ4" t="n">
         <v>1</v>
@@ -24859,68 +24695,68 @@
         <v>1</v>
       </c>
       <c r="AV4" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW4" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AX4" t="n">
         <v>6</v>
       </c>
       <c r="AY4" t="n">
-        <v>5.005231198953302</v>
+        <v>4.97130613733782</v>
       </c>
       <c r="AZ4" t="n">
-        <v>0.994768801046698</v>
+        <v>1.02869386266218</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>TCE-RJ</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.4407467228894335</v>
+        <v>0.3787705980140124</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Intermediário</t>
+          <t>Iniciando</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.4331568546537495</v>
+        <v>0.5038560968632533</v>
       </c>
       <c r="E5" t="n">
-        <v>0.4480724791053855</v>
+        <v>0</v>
       </c>
       <c r="F5" t="n">
-        <v>0.2392146296411173</v>
+        <v>0.0509979803806467</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6738474634857513</v>
+        <v>0.0502282515626283</v>
       </c>
       <c r="H5" t="n">
-        <v>0.715498338063645</v>
+        <v>0.7986485052829118</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3250000000000001</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K5" t="n">
-        <v>0.3198595250632113</v>
+        <v>0.4061196989022282</v>
       </c>
       <c r="L5" t="n">
-        <v>0.3382302099500095</v>
+        <v>0.2952920839800037</v>
       </c>
       <c r="M5" t="n">
-        <v>0.4476883776441789</v>
+        <v>0.264368039119223</v>
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>ISP</t>
+          <t>TCE-RJ</t>
         </is>
       </c>
       <c r="O5" t="n">
@@ -24960,10 +24796,10 @@
         <v>1</v>
       </c>
       <c r="AA5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC5" t="n">
         <v>1</v>
@@ -24972,7 +24808,7 @@
         <v>1</v>
       </c>
       <c r="AE5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF5" t="n">
         <v>1</v>
@@ -24984,10 +24820,10 @@
         <v>0</v>
       </c>
       <c r="AI5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AJ5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK5" t="n">
         <v>1</v>
@@ -25005,7 +24841,7 @@
         <v>1</v>
       </c>
       <c r="AP5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AQ5" t="n">
         <v>1</v>
@@ -25014,10 +24850,10 @@
         <v>1</v>
       </c>
       <c r="AS5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU5" t="n">
         <v>1</v>
@@ -25032,20 +24868,20 @@
         <v>6</v>
       </c>
       <c r="AY5" t="n">
-        <v>5.006948750922162</v>
+        <v>5.106462042780931</v>
       </c>
       <c r="AZ5" t="n">
-        <v>0.9930512490778378</v>
+        <v>0.8935379572190687</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>TCE-RJ</t>
+          <t>MESQUITA</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.3787705980140124</v>
+        <v>0.3781599689108759</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -25053,38 +24889,38 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.5038560968632533</v>
+        <v>0.467407194199117</v>
       </c>
       <c r="E6" t="n">
         <v>0</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0509979803806467</v>
+        <v>0.208847793116929</v>
       </c>
       <c r="G6" t="n">
-        <v>0.0502282515626283</v>
+        <v>0.5771681432224739</v>
       </c>
       <c r="H6" t="n">
-        <v>0.7986485052829118</v>
+        <v>0.9331729051917952</v>
       </c>
       <c r="I6" t="n">
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.04166666666666666</v>
       </c>
       <c r="K6" t="n">
-        <v>0.4061196989022282</v>
+        <v>0.04686802611500751</v>
       </c>
       <c r="L6" t="n">
-        <v>0.2952920839800037</v>
+        <v>0.04999999999999995</v>
       </c>
       <c r="M6" t="n">
-        <v>0.264368039119223</v>
+        <v>0.2965349121203979</v>
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>TCE-RJ</t>
+          <t>MESQUITA</t>
         </is>
       </c>
       <c r="O6" t="n">
@@ -25109,16 +24945,16 @@
         <v>1</v>
       </c>
       <c r="V6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z6" t="n">
         <v>1</v>
@@ -25127,7 +24963,7 @@
         <v>0</v>
       </c>
       <c r="AB6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC6" t="n">
         <v>1</v>
@@ -25160,7 +24996,7 @@
         <v>1</v>
       </c>
       <c r="AM6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN6" t="n">
         <v>1</v>
@@ -25178,38 +25014,38 @@
         <v>1</v>
       </c>
       <c r="AS6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT6" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU6" t="n">
         <v>1</v>
       </c>
       <c r="AV6" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW6" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX6" t="n">
         <v>6</v>
       </c>
       <c r="AY6" t="n">
-        <v>5.135869630830648</v>
+        <v>5.107793686692037</v>
       </c>
       <c r="AZ6" t="n">
-        <v>0.8641303691693523</v>
+        <v>0.8922063133079625</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>MESQUITA</t>
+          <t>AGENERSA</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.3781599689108759</v>
+        <v>0.3556247825995705</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -25217,38 +25053,38 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.467407194199117</v>
+        <v>0.3032905664772133</v>
       </c>
       <c r="E7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F7" t="n">
-        <v>0.208847793116929</v>
+        <v>0.1553157624419259</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5771681432224739</v>
+        <v>0.2759460083070382</v>
       </c>
       <c r="H7" t="n">
-        <v>0.9331729051917952</v>
+        <v>0.4499274133891529</v>
       </c>
       <c r="I7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="J7" t="n">
-        <v>0.04166666666666666</v>
+        <v>0.2666666666666668</v>
       </c>
       <c r="K7" t="n">
-        <v>0.04686802611500751</v>
+        <v>0.2730944416681872</v>
       </c>
       <c r="L7" t="n">
-        <v>0.04999999999999995</v>
+        <v>0.3509621739585792</v>
       </c>
       <c r="M7" t="n">
-        <v>0.2965349121203979</v>
+        <v>0.4034893895862416</v>
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>MESQUITA</t>
+          <t>AGENERSA</t>
         </is>
       </c>
       <c r="O7" t="n">
@@ -25273,16 +25109,16 @@
         <v>1</v>
       </c>
       <c r="V7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="W7" t="n">
         <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z7" t="n">
         <v>1</v>
@@ -25294,19 +25130,19 @@
         <v>0</v>
       </c>
       <c r="AC7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AE7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF7" t="n">
         <v>1</v>
       </c>
       <c r="AG7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH7" t="n">
         <v>0</v>
@@ -25315,7 +25151,7 @@
         <v>1</v>
       </c>
       <c r="AJ7" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK7" t="n">
         <v>1</v>
@@ -25324,7 +25160,7 @@
         <v>1</v>
       </c>
       <c r="AM7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN7" t="n">
         <v>1</v>
@@ -25354,26 +25190,26 @@
         <v>0</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>15</v>
       </c>
       <c r="AX7" t="n">
         <v>6</v>
       </c>
       <c r="AY7" t="n">
-        <v>5.13713984321376</v>
+        <v>5.156937829155866</v>
       </c>
       <c r="AZ7" t="n">
-        <v>0.8628601567862404</v>
+        <v>0.8430621708441342</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>AGENERSA</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.3556247825995705</v>
+        <v>0.3436749796527468</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -25381,38 +25217,38 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.3032905664772133</v>
+        <v>0.3083610594283083</v>
       </c>
       <c r="E8" t="n">
-        <v>1</v>
+        <v>0.7019275208946145</v>
       </c>
       <c r="F8" t="n">
-        <v>0.1553157624419259</v>
+        <v>0.3674641240965996</v>
       </c>
       <c r="G8" t="n">
-        <v>0.2759460083070382</v>
+        <v>0.2231695591640398</v>
       </c>
       <c r="H8" t="n">
-        <v>0.4499274133891529</v>
+        <v>0.352918884966675</v>
       </c>
       <c r="I8" t="n">
         <v>0.5</v>
       </c>
       <c r="J8" t="n">
-        <v>0.2666666666666668</v>
+        <v>0.4416666666666667</v>
       </c>
       <c r="K8" t="n">
-        <v>0.2730944416681872</v>
+        <v>0.4391741411168048</v>
       </c>
       <c r="L8" t="n">
-        <v>0.3509621739585792</v>
+        <v>0.1778865218757386</v>
       </c>
       <c r="M8" t="n">
-        <v>0.4034893895862416</v>
+        <v>0.3759729108713883</v>
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>AGENERSA</t>
+          <t>FS</t>
         </is>
       </c>
       <c r="O8" t="n">
@@ -25437,16 +25273,16 @@
         <v>1</v>
       </c>
       <c r="V8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="W8" t="n">
         <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z8" t="n">
         <v>1</v>
@@ -25455,16 +25291,16 @@
         <v>0</v>
       </c>
       <c r="AB8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AC8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD8" t="n">
         <v>0</v>
       </c>
       <c r="AE8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AF8" t="n">
         <v>1</v>
@@ -25473,7 +25309,7 @@
         <v>0</v>
       </c>
       <c r="AH8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AI8" t="n">
         <v>1</v>
@@ -25488,7 +25324,7 @@
         <v>1</v>
       </c>
       <c r="AM8" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AN8" t="n">
         <v>1</v>
@@ -25503,13 +25339,13 @@
         <v>1</v>
       </c>
       <c r="AR8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AS8" t="n">
         <v>1</v>
       </c>
       <c r="AT8" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU8" t="n">
         <v>1</v>
@@ -25518,26 +25354,26 @@
         <v>0</v>
       </c>
       <c r="AW8" t="n">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="AX8" t="n">
         <v>6</v>
       </c>
       <c r="AY8" t="n">
-        <v>5.184016863259705</v>
+        <v>5.182997645583422</v>
       </c>
       <c r="AZ8" t="n">
-        <v>0.8159831367402948</v>
+        <v>0.8170023544165783</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>GSI</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.3436749796527468</v>
+        <v>0.334377486284863</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -25545,38 +25381,38 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.3083610594283083</v>
+        <v>0.2344301251162085</v>
       </c>
       <c r="E9" t="n">
-        <v>0.7019275208946145</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F9" t="n">
-        <v>0.3674641240965996</v>
+        <v>0.3537436754376</v>
       </c>
       <c r="G9" t="n">
-        <v>0.2231695591640398</v>
+        <v>0.6052823722694305</v>
       </c>
       <c r="H9" t="n">
-        <v>0.352918884966675</v>
+        <v>0.2560097569435651</v>
       </c>
       <c r="I9" t="n">
         <v>0.5</v>
       </c>
       <c r="J9" t="n">
-        <v>0.4416666666666667</v>
+        <v>0.6333333333333333</v>
       </c>
       <c r="K9" t="n">
-        <v>0.4391741411168048</v>
+        <v>0.2380300152594287</v>
       </c>
       <c r="L9" t="n">
-        <v>0.1778865218757386</v>
+        <v>0.2358762519400116</v>
       </c>
       <c r="M9" t="n">
-        <v>0.3759729108713883</v>
+        <v>0.4257888327452301</v>
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>FS</t>
+          <t>GSI</t>
         </is>
       </c>
       <c r="O9" t="n">
@@ -25601,34 +25437,34 @@
         <v>1</v>
       </c>
       <c r="V9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z9" t="n">
         <v>1</v>
       </c>
       <c r="AA9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AC9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD9" t="n">
         <v>0</v>
       </c>
       <c r="AE9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AF9" t="n">
         <v>1</v>
@@ -25637,7 +25473,7 @@
         <v>0</v>
       </c>
       <c r="AH9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AI9" t="n">
         <v>1</v>
@@ -25652,7 +25488,7 @@
         <v>1</v>
       </c>
       <c r="AM9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AN9" t="n">
         <v>1</v>
@@ -25670,10 +25506,10 @@
         <v>0</v>
       </c>
       <c r="AS9" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU9" t="n">
         <v>1</v>
@@ -25682,26 +25518,26 @@
         <v>0</v>
       </c>
       <c r="AW9" t="n">
-        <v>18</v>
+        <v>14</v>
       </c>
       <c r="AX9" t="n">
         <v>6</v>
       </c>
       <c r="AY9" t="n">
-        <v>5.208874485670501</v>
+        <v>5.203273374939098</v>
       </c>
       <c r="AZ9" t="n">
-        <v>0.7911255143294991</v>
+        <v>0.7967266250609022</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>GSI</t>
+          <t>QUEIMADOS</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>0.334377486284863</v>
+        <v>0.2902940949541311</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -25709,38 +25545,38 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.2344301251162085</v>
+        <v>0.2744907033325922</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9153816527369236</v>
+        <v>0.3863678633452264</v>
       </c>
       <c r="F10" t="n">
-        <v>0.3537436754376</v>
+        <v>0.1818535108110998</v>
       </c>
       <c r="G10" t="n">
-        <v>0.6052823722694305</v>
+        <v>0.2817691859871062</v>
       </c>
       <c r="H10" t="n">
-        <v>0.2560097569435651</v>
+        <v>0.5267891414886573</v>
       </c>
       <c r="I10" t="n">
         <v>0.5</v>
       </c>
       <c r="J10" t="n">
-        <v>0.6333333333333333</v>
+        <v>0.3250000000000001</v>
       </c>
       <c r="K10" t="n">
-        <v>0.2380300152594287</v>
+        <v>0.2605707583149178</v>
       </c>
       <c r="L10" t="n">
-        <v>0.2358762519400116</v>
+        <v>0.2226460419900018</v>
       </c>
       <c r="M10" t="n">
-        <v>0.4257888327452301</v>
+        <v>0.3047477962812494</v>
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>GSI</t>
+          <t>QUEIMADOS</t>
         </is>
       </c>
       <c r="O10" t="n">
@@ -25765,28 +25601,28 @@
         <v>1</v>
       </c>
       <c r="V10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10" t="n">
         <v>1</v>
       </c>
       <c r="AA10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AB10" t="n">
         <v>0</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD10" t="n">
         <v>0</v>
@@ -25798,7 +25634,7 @@
         <v>1</v>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH10" t="n">
         <v>0</v>
@@ -25807,7 +25643,7 @@
         <v>1</v>
       </c>
       <c r="AJ10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK10" t="n">
         <v>1</v>
@@ -25831,41 +25667,41 @@
         <v>1</v>
       </c>
       <c r="AR10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AS10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AT10" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU10" t="n">
         <v>1</v>
       </c>
       <c r="AV10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AX10" t="n">
         <v>6</v>
       </c>
       <c r="AY10" t="n">
-        <v>5.228214853083601</v>
+        <v>5.299409276986614</v>
       </c>
       <c r="AZ10" t="n">
-        <v>0.7717851469163985</v>
+        <v>0.7005907230133861</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>QUEIMADOS</t>
+          <t>CEPERJ</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>0.2902940949541311</v>
+        <v>0.2580680375751482</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -25873,38 +25709,38 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.2744907033325922</v>
+        <v>0</v>
       </c>
       <c r="E11" t="n">
-        <v>0.3863678633452264</v>
+        <v>0.9153816527369236</v>
       </c>
       <c r="F11" t="n">
-        <v>0.1818535108110998</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.2817691859871062</v>
+        <v>0.5</v>
       </c>
       <c r="H11" t="n">
-        <v>0.5267891414886573</v>
+        <v>0.3336996655614665</v>
       </c>
       <c r="I11" t="n">
-        <v>0.5</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>0.3250000000000001</v>
+        <v>0.2666666666666666</v>
       </c>
       <c r="K11" t="n">
-        <v>0.2605707583149178</v>
+        <v>0.2617809480474065</v>
       </c>
       <c r="L11" t="n">
-        <v>0.2226460419900018</v>
+        <v>0.4999999999999994</v>
       </c>
       <c r="M11" t="n">
-        <v>0.3047477962812494</v>
+        <v>0.4940957477347167</v>
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>QUEIMADOS</t>
+          <t>CEPERJ</t>
         </is>
       </c>
       <c r="O11" t="n">
@@ -25929,28 +25765,28 @@
         <v>1</v>
       </c>
       <c r="V11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="W11" t="n">
         <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z11" t="n">
         <v>1</v>
       </c>
       <c r="AA11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB11" t="n">
         <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
         <v>0</v>
@@ -25962,7 +25798,7 @@
         <v>1</v>
       </c>
       <c r="AG11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
         <v>0</v>
@@ -25971,7 +25807,7 @@
         <v>1</v>
       </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AK11" t="n">
         <v>1</v>
@@ -26007,29 +25843,29 @@
         <v>1</v>
       </c>
       <c r="AV11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW11" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX11" t="n">
         <v>6</v>
       </c>
       <c r="AY11" t="n">
-        <v>5.31991580423426</v>
+        <v>5.369687016562511</v>
       </c>
       <c r="AZ11" t="n">
-        <v>0.6800841957657404</v>
+        <v>0.6303129834374888</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>CEPERJ</t>
+          <t>CODIN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>0.2580680375751482</v>
+        <v>0.2460470495950194</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -26037,38 +25873,38 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0</v>
+        <v>0.2235205846062349</v>
       </c>
       <c r="E12" t="n">
-        <v>0.9153816527369236</v>
+        <v>0.6814368103037126</v>
       </c>
       <c r="F12" t="n">
-        <v>0.5</v>
+        <v>0.03936242287996428</v>
       </c>
       <c r="G12" t="n">
-        <v>0.5</v>
+        <v>0.192323654976707</v>
       </c>
       <c r="H12" t="n">
-        <v>0.3336996655614665</v>
+        <v>0.352918884966675</v>
       </c>
       <c r="I12" t="n">
         <v>0</v>
       </c>
       <c r="J12" t="n">
-        <v>0.2666666666666666</v>
+        <v>0.2999999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.2617809480474065</v>
+        <v>0.2281526269588791</v>
       </c>
       <c r="L12" t="n">
-        <v>0.4999999999999994</v>
+        <v>0.1655155321114064</v>
       </c>
       <c r="M12" t="n">
-        <v>0.4940957477347167</v>
+        <v>0.2666496395137506</v>
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>CEPERJ</t>
+          <t>CODIN</t>
         </is>
       </c>
       <c r="O12" t="n">
@@ -26093,7 +25929,7 @@
         <v>1</v>
       </c>
       <c r="V12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="W12" t="n">
         <v>0</v>
@@ -26102,7 +25938,7 @@
         <v>1</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12" t="n">
         <v>1</v>
@@ -26126,7 +25962,7 @@
         <v>1</v>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AH12" t="n">
         <v>0</v>
@@ -26162,10 +25998,10 @@
         <v>1</v>
       </c>
       <c r="AS12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AT12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AU12" t="n">
         <v>1</v>
@@ -26174,26 +26010,26 @@
         <v>0</v>
       </c>
       <c r="AW12" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AX12" t="n">
         <v>6</v>
       </c>
       <c r="AY12" t="n">
-        <v>5.386951484209912</v>
+        <v>5.395902071441158</v>
       </c>
       <c r="AZ12" t="n">
-        <v>0.613048515790088</v>
+        <v>0.6040979285588417</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>CODIN</t>
+          <t>SECTI</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>0.2460470495950194</v>
+        <v>0.2411373679833352</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -26201,38 +26037,38 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.2235205846062349</v>
+        <v>0.1216576931116455</v>
       </c>
       <c r="E13" t="n">
-        <v>0.6814368103037126</v>
+        <v>0.3285182893742963</v>
       </c>
       <c r="F13" t="n">
-        <v>0.03936242287996428</v>
+        <v>0.15</v>
       </c>
       <c r="G13" t="n">
-        <v>0.192323654976707</v>
+        <v>0.4032683763560195</v>
       </c>
       <c r="H13" t="n">
-        <v>0.352918884966675</v>
+        <v>0.9400037895556652</v>
       </c>
       <c r="I13" t="n">
         <v>0</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2999999999999999</v>
+        <v>0.5499999999999998</v>
       </c>
       <c r="K13" t="n">
-        <v>0.2281526269588791</v>
+        <v>0.2551776115277979</v>
       </c>
       <c r="L13" t="n">
-        <v>0.1655155321114064</v>
+        <v>0.0736082159485815</v>
       </c>
       <c r="M13" t="n">
-        <v>0.2666496395137506</v>
+        <v>0.3504128688766328</v>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>CODIN</t>
+          <t>SECTI</t>
         </is>
       </c>
       <c r="O13" t="n">
@@ -26257,7 +26093,7 @@
         <v>1</v>
       </c>
       <c r="V13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="W13" t="n">
         <v>0</v>
@@ -26266,7 +26102,7 @@
         <v>1</v>
       </c>
       <c r="Y13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
         <v>1</v>
@@ -26278,10 +26114,10 @@
         <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AE13" t="n">
         <v>0</v>
@@ -26290,7 +26126,7 @@
         <v>1</v>
       </c>
       <c r="AG13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
         <v>0</v>
@@ -26299,7 +26135,7 @@
         <v>1</v>
       </c>
       <c r="AJ13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AK13" t="n">
         <v>1</v>
@@ -26329,7 +26165,7 @@
         <v>0</v>
       </c>
       <c r="AT13" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AU13" t="n">
         <v>1</v>
@@ -26338,16 +26174,16 @@
         <v>0</v>
       </c>
       <c r="AW13" t="n">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="AX13" t="n">
         <v>6</v>
       </c>
       <c r="AY13" t="n">
-        <v>5.411957183596291</v>
+        <v>5.406608976156456</v>
       </c>
       <c r="AZ13" t="n">
-        <v>0.5880428164037088</v>
+        <v>0.5933910238435436</v>
       </c>
     </row>
   </sheetData>
